--- a/runtime/downloaded/Новая таблица (25).xlsx
+++ b/runtime/downloaded/Новая таблица (25).xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<s:workbook xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <s:workbookPr/>
   <s:bookViews>
     <s:workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
@@ -9,7 +9,7 @@
     <s:sheet name="замена" sheetId="1" state="visible" r:id="rId1"/>
   </s:sheets>
   <s:definedNames>
-    <s:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">замена!$A$1:$D$75</s:definedName>
+    <s:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">замена!$A$1:$D$77</s:definedName>
     <s:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">замена!$A$1:$D$76</s:definedName>
     <s:definedName name="Диапазон_2">#REF!</s:definedName>
   </s:definedNames>
@@ -9301,11 +9301,1182 @@
   <s:si>
     <s:t>ОД.4 Индивидуальный проект Елхова Г.А. УЛК2,ауд.114</s:t>
   </s:si>
+  <s:si>
+    <s:t>ОД.03 История Степанова С.С. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 28.05 по 10.06 С 1 по 3(УЛК1,ауд.405)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 30.05 по 20.06 с 1 по 3 пары (УЛК2,ауд.308)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 02.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 01.06 по 20.06 с 2 по 4 (УЛК1,ауд.312)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.  07 Математика  Трофимчук Д.В. УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 14 Индивидуальный проект Шевчук О.П.УЛК2,ауд.311 </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11Физика Быкова С.В.   УЛК2,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика Быкова С.В. УЛК2,ауд.303</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 14 Индивидуальный проект Елхова Г.А. УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02  Литература Галицкова А.В.  УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.14 Индивидуальный проект             Степанова С.С. УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.05 география Веледеева А.Г. УЛК2,ауд.114</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.14 Индивидуальный проект    Степанова С.С. УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.03 Информационные технологии Дерябкина Е.В. УЛК1,Ауд.408</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.03 Информационные технологии Дерябкина Е.В. УЛК1,Ауд.402</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 09.02 Оптимизация веб-приложений Савченко А.И. УЛК2.ауд.408</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.06 Информационные технологии в профессиональной деятельности Дерябкина Е.В   УЛК1,ауд.401</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК  01.01 Проектирование зданий и сооружений силина Е.М. УЛК1,ауд.410</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01 Организация технологических процессов на объекте капитального строительства Коплык В.Л. УЛК1,ауд.3309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.01 Основы философии Мандрова О.А. УЛК1,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СЭЭЗ-Д31</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Швецова Д.А,</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Масленников А.Б.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Савченко А.И,</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 25.05 по 06.06 с 4 по6 (УЛК1,ауд.016)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 25.05 по 06.06 с 4 по 6 (УЛК1,ауд.016)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.06 Информационные технологии в профессиональной деятельности Дерябкина Е.В   УЛК1,ауд.402</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.01 Основы философии Мандрова О.А. УЛК1,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 03.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 30.05 по 20.06 с 3 по 5 пары (УЛК2,ауд.310)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>М</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.03 История  Степанова С.С.  УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.  07 Математика  Быкова С.В. УЛК2,ауд.303</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика        Савченко А.И.  УЛК1,ауд.407</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 История    Степанова С.С. УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика  Иванов С.А.  УЛК2,ауд.202</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.03 История  Маркитан А.Л. УЛК2,ауд.210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.03 История  Маркитан А.Л. УЛК2,ауд.211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Обеспечение ведения управления  МКД и домашним хозяйством Кузнецов А.В. УЛК1,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.05 Основы финансовой грамотности Пухляр И.Н. УЛК1,ауд.013</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОСГЭ.05 Физическая культура Шумахова И.Д. с/з2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Проект производства работ  Коплык В.Л. УЛК1,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.01  Монтажник каркасно-обшивных  конструкций Силина Е.М. УЛК1.ауд.410</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Проект производства работ  Сызранцев В.В. УЛК1,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК  02.02 Управление и  контроль строительного производства инженерных сооружений Чубцов К.В. УЛК1,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Маркитан А.Л.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>С 30.05 по 20.06 с 3 по 5 пары (УЛК1,ауд.017)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 30.05 по 20.06 с 3 по 5 пары (УЛК1,ауд.411)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 04.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 30.05 по 20.06 с 1 по 3 пары (УЛК2,ауд.309)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 Истори Степанова С.С.      УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.  04 Обществознание  Коскина Е.В. Общ.1-акт.зал</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.12 Химия    Коробкова М.Н.УЛК2,ауд.208</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Проект производства работ   Сызранцев В.В. УЛК1,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.02 Организация работы складского хозяйства  Петрова Т.Н. УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 04.01 Организация материально-технического обеспечения  Чубцов К.В. УЛК1,ауд.307         </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.02 Организация работы складского хозяйства убцов К.В. УЛК1,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 История    Степанова С.С. УЛК2,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.13 Биология  Царегородцева Н.А.   УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 05.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>С 30.05 по 20.06 с 1 по 3 пары (УЛК1,ауд.405)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 30.05 по 20.06 с 3 по 4 пары (УЛК1,ауд.409)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 28.05 по 10.06 С 1 по 3 (УЛК1,ауд.020)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика    Соловьева Т.А. УЛК2,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11Физика Елхов Н.А.  УЛК2,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02
+  Литература Галицкова А.В.  УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.14 Инд. проект Шевчук О.П.  УЛК2,ауд.311</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.
+  07 Математика Иванова И.В. УЛК2,ауд.114</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература  Семенова О.В.   УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.13  Биология    Царегородцева Н.А.   УЛК2,ауд.207</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Эксплуатация зданий  и сооружений Петрова Т.Н.УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Эксплуатация зданий  и сооружений Чубцов К.В. УЛК1,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Проектирование зданий и сооружений Бурлуцкий УПМ-209</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01 Организация технологических процессов на объекте капитального строительства Арзамасцев Г.А. УПМ-111</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.04 Физическая культура Масленников А.Е, спорт. площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 УЛК1,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Проект производства работ Коплык В.Л. УЛК1,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 28.05 по 10.06 С 1 по 3 (УЛК1,ауд.405)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 06.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 30.05 по 20.06 с 1 по 3 пары (УЛК1,ауд.409)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика  Савченко А.И. УЛК1,ауд.407</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 История  Отт А.А. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЕН.03  Теория вероятностей и математическая статистика Закарян В.Г. УЛК2,Ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК
+  01.01 Проектирование зданий и сооружений Арзамасцев Г.А. УПМ-111</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Организация материально-технического обеспечения Чубцов К.В. УЛК1,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 07.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 08.06 по 27.06 (</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Пышьева  О.В.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 08.06 по 27.06 (УПМ-204)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 08.06 по 20.06</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 08.06 по 27.06</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 04.06 по по 24.06</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика  Володькина Т.В. УЛК2,ауд.205</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.13 Биология  Мельничук Е.С. УЛК203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.12 Химия Мельничук Е.С. УЛК203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.12 Химия Мельничук Е.С. УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.13 Биология  Мельничук Е.С. УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература Семенова О.В.  УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11 Физика  Швецова Д.А.УЛК2,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.03 История Маркитан А.Л.. УЛК2,ауд.210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11Физика Елхов Н.А.   УЛК2,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02  Литература    Анищенко Е.А. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК  08.02 Графический дизайн и мультимедиа Савченко А.И. УЛК1,ауд210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК  08.02 Графический дизайн и мультимедиа Савченко А.И. УЛК1,ауд407</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.13 Биология  Мельничук Е.С. УЛК2,ауд.114</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.12 Химия Мельничук Е.С. УЛК2,ауд.114</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 08.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>С 30.05 по 20.06  с 2 по 4 пары (УПМ-111)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 09.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 14 Индивидуальный проект Шевчук О.П.УЛК2,ауд.311  </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.13 Биология   Мельничук Е.С. УЛК2,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.06 Иностранный язык                                               
+  Отт А.А. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.06 Иностранный язык   Отт А.А. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 14 Индивидуальный проект Степанова С.С. УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 11 Физика  Швецова Д.А.УЛК2,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>С 30.05 по 20.06 с 4 по 6 пары (УЛК1,ауд.017)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 10.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.14 Индивидуальный проект Елхова Г.А. УЛК2,ауд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.14 Индивидуальный проект Елхова Г.А. УЛК2,ауд.211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.03 История Степанова С.С. УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература Елхова Г.А. УЛК2,ауд.211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 11 Физика Киргинцев Д.Е. УЛК1,ауд.017</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература Стафеева Е.М. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК  08.01 Проектирование и разработка интерфейсов пользователя Шишанова Т.В. УЛК1,Ауд.408</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Эксплуатация зданий  и сооружений   Чубцов К.В.  УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Эксплуатация зданий  и сооружений   Чубцов К.В.  УЛК1,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Разработка кода информационных систем</s:t>
+  </s:si>
+  <s:si>
+    <s:r>
+      <s:rPr>
+        <s:sz val="14"/>
+        <s:vertAlign val="baseline"/>
+        <s:scheme val="minor"/>
+      </s:rPr>
+      <s:t>МДК 05.02 Разработка кода информационных систем Насонова Н.А. УЛК1,ауд.402</s:t>
+    </s:r>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 11.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика    Шевчук О.П.    УЛК2,ауд.311</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература Стафеева Е.М.  УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 История   Чаплыгина Н.А. УЛК2,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика  Закарян В.Г.. УЛК2,ауд.210</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 10 Основы безопасности и защиты Родины Карнаухов В.В. УЛК2,ауд.304    </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 11 Физика    Киргинцев Д.Е. УЛК1,ауд.017</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 11 Физика Швецова Д.А.УЛК2,ауд.305 </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 История Маркитан А.Л. УЛК2,ауд.210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 11 Физика    Киргинцев Д.Е. УЛК1,ауд.211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Савечнко А.И.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>С 1 по 3 (УЛК1,ауд.020)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ДОУ=Д51</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.13 Биология Царегородцева Н.А.  УЛК2,ауд.207     </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 09 Физическая культура    Стадник А.П.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература  Галицкова А.В, УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика  Соловьева Т.А. УЛК2,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.05 География Веледеева А.Г. УЛК2,ауд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика Иванова И.В.  УЛК2,ауд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 07 Математика Иванова И.В.  </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература Стафеева Е.М.   УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.  09 Физическая культура  Масленников А.Е.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.13 Биология Веледеева А.Г.  </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.05 География Веледеева А.Г. </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 08 Информатика Шевчук О.П. УЛК2,ауд.311  </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 14 Индивидуальный проект Елхова Г.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.02 Разработка кода информационных систем Насонова Н.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.01 Проектирование и дизайн информационных систем Насонова Н.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Проектирование зданий и сооружений Сызранцев В.В.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОП.10 Финансовая грамотность Шевцова В.А. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 13.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 15.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 15.06 по .06</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 15.06 по 27.06</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02  Литература Стафеева Е.М.   УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11  Физика  Трофимчук Д.В. УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.03 История  Степанова С.С. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.  03 История   Отт А.А. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК  01.02 Проект производства работ   Сызранцев В.В. УЛК1,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК
+  02.01 Организация технологических процессов на объекте капитального
+  строительства Коплык В.Л. УЛК1,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Елхоа Г.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 16.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>С 11.06 по 24.06</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.14 Индивидуальный проект Степанова С.С. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Трофимчук Д.В. УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика Трофимчук Д.В. УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 14 Индивидуальный проект
+Шевчук О.П.УЛК2,ауд.311    </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 14 Индивидуальный проект Шевчук О.П.УЛК2,ауд.311    </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ООД. 07 Математика Быкова С.В. УЛК2,ауд.303</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 14 Индивидуальный проект Елхова Г.А.УЛК2,ауд.110   </s:t>
+  </s:si>
+  <s:si>
+    <s:t>С 30.05 по 20.06  с 3 по 5 пары (УПМ-111)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика Иванова И.В.УЛК2,ауд.202а</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 03 История Чаплыгина Н.А. УЛК2,ауд.308   </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.14 Индивидуальный проект Степанова С.С. УЛК2,ауд.306 </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.13 Биология Царегородцева Н.А. УЛК2,ауд.211   </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 14 Инд. Проект                                                Маркитан О.А. УЛК2,ауд.210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 14 Индивидуальный проект Маркитан О.А. УЛК2,ауд.210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 14 История Маркитан О.А. УЛК2,ауд.210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература Семенова О.В. УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.12 Химия Коробкова М.Н.УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.03 Тестирование информационных систем Александрова Л.В.УЛК1,ауд.406</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК1, ауд.407</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 09.02 Оптимизация веб-приложений Савченко А.И. УЛК2.ауд.210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 09.02 Оптимизация веб-приложений Савченко А.И. УЛК2.ауд.407</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Учёт и контроль технологических процессов на объекте капитального строительства Силина Е.М. УЛК1, ауд.410</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.05 География Сапрыкина О.С.  УЛК2,ауд.114</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 10 Основы безопасности и защиты Родины Карнаухов В.В. УЛК2,ауд.303</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 01.06 по 20.06 с 3 по 5 (УЛК1,ауд.312)</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.14 История Степанова С.С. УЛК2,ауд.306 </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.05 География Царегородцева Н.А. ЛК2,ауд.207</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11Физика Пошарникова К.С.УЛК2,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.13 Биология Мельничук Е.С. УЛК2, ауд. 307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.12 Химия     Мельничук Е.С. УЛК2, ауд. 307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК2, ауд. 211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 09 Физическая культура Стадник А.П. с/площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК2, ауд. 110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература Елхова Г.А.УЛК2,ауд. 110</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.14 Индивидуальный проект  Маркитан А.Л. УЛК2,ауд.210        </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература Стафеева Е.М.УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.02 Разработка кода информационных систем
+Насонова Н.А.УЛК1,ауд.402</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК1, спортивная площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.03 Информационные технологии                        Дерябкина Е.В. УЛК1,Ауд.401</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.03 Информационные технологии  Дерябкина Е.В. УЛК1,Ауд.401</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Управление деятельностью структурных подразделений при выполнении строительно-монтажных работ, в том числе  отделочных работ эксплуатации, ремонте  и реконструкции зданий и сооружений Петрова Т.Н. УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Проектирование зданий и сооружений Сызранцев В.В.УЛК1, 306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 17.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 18.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">с 18.05 по 04.07 </s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 30.05 по 20.06 с 3 по 6 пары (УЛК1,ауд.409)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.05 География Царегородцева Н.А. УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика Быкова С.В. УЛК2,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК2, ауд. 306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика Закарян В.Г. УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК2, ауд. 108</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 10 Основы безопасности и защиты Родины Каранухов В.В. УЛК2,ауд.304 </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература    Галицкова А.В. УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.05 География  Веледеева А.Г. УЛК2,ауд. 114</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК1, ауд. 401</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК1, ауд. 407</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Учёт и контроль технологических процессов на объекте капитального строительства Силина Е.М. УПМ-308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02  Литература Стафеева Е.М., УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 11 Физика  Швецова Д.А.УЛК2,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература Галицкова   УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.  07 Математика   Закарян В.Г. УЛК2,ауд.202</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 09 Физическая культура  Стадник А.П. т/з</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 12 Химия Коробкова М.Н.  УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература    Елхова Г.А.  УЛК2,ауд.108</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика Шевчук О.П. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.14 Индивидуальный проект  Маркитан А.Л. УЛК2,ауд.210     </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11 Физика  Киргинцев Д.Е. УПМ-211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11Физика Елхов Н.А.  УЛК2,ауд.30</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК05.03 Тестирование информационных систем Александрова Л.В. УЛК1,ауд.406</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 19.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК05.03 Тестирование информационных систем Александрова Л.В. УЛК1,ауд.401</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 20.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11Физика Елхов Н.А.  УЛК2,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика   Трофимчук Д.В. УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.13 Биология Царегородцева Н.А.  УЛК2,ауд.207        </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.13 Биология Царегородцева Н.А.  УЛК2,ауд.211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11Физика  Швецова Д.А.  УЛК2,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02 Литература  Галицкова А.В. УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.12 Химия   Мельничук Е.С. УЛК2,ауд.202а</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика Иванова И.В. УЛК2,ауд.114</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.02  Литература  Стафеева Е.М.  УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 14 Инд. проектСтепанова С.С. УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve"> </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 14 Инд. проект Степанова С.С. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve"> ОД. 09 Физическая культура  Стадник А.П. спорт.площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 11 Физика   Киргинцев Д.Е. УПМ-211</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 05.02 Разработка кода информационных систем Насонова Н.А. УЛК1,ауд.402 </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 08.02 Графический дизайн и мультимедиа Савченко А.И. УЛК1,ауд210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Эксплуатация зданий  и сооружений   Петрова Т.Н. УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика  Быкова С.В. УЛК2,ауд.303</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК04.01 Эксплуатация зданий  и сооружений  Петрова Т.Н. УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 22.06 (знаменатель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 22.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК.02.02  Учёт и контроль технологических процессов на объекте капитального строительства Силина Е.М.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК.02.02  Учёт и контроль технологических процессов на объекте капитального строительства УЛК1ауд.410 Силина Е.М.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК.01.01 Проектирование зданий и сооружений Сызранцев В.В. УЛК1,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК.02.02 Учёт и  контроль технологических процессов на объекте капитального строительства Силина Е.М. УЛК1,ауд.410</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 23.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК.01.01 Проектирование зданий и сооружений Сызранцев В.В. УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 24.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 25.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК.02.02  Учет и контроль тех. процессов на объекте кап. строительства Силина Е.М. УЛК1,ауд.410</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК.03.01 Управление деятельностью структурных подразделений при выполнении строительно-монтажных
+  работ, в том числе  отделочных работэксплуатации, ремонте  и реконструкции зданий и сооружений УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК.03.01 Управление деятельностью структурных подразделений при выполнении строительно-монтажных
+  работ, в том числе  отделочных работэксплуатации, ремонте  и реконструкции зданий и сооружений Петрова Т.Н. УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 26.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 04.01 Эксплуатация зданий  и сооружений </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Эксплуатация зданий  и сооружений Петрова Т.Н. УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 27.06 (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА  (числитель)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 12.09 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ПГ-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ПГ-Д63</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ПГ-Д64</s:t>
+  </s:si>
+  <s:si>
+    <s:t>РУПО-Д63</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СЭЗ-61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОМД-61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.06 Иностранный язык
+   ВАКАНСИЯ</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.06 Иностранный язык Толызенкова А.А. УЛК2,ауд.202а</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.06 Информационные технологии в профессиональной деятельности
+   Дерябкина Е.В. УЛК1,ауд.401</s:t>
+  </s:si>
+  <s:si>
+    <s:r>
+      <s:rPr>
+        <s:sz val="14"/>
+        <s:vertAlign val="baseline"/>
+        <s:scheme val="minor"/>
+      </s:rPr>
+      <s:t>ОП.06 Информационные технологии в профессиональной деятельности
+   Дерябкина Е.В. УЛК1,ауд.401</s:t>
+    </s:r>
+  </s:si>
+  <s:si>
+    <s:r>
+      <s:rPr>
+        <s:sz val="14"/>
+        <s:vertAlign val="baseline"/>
+        <s:scheme val="minor"/>
+      </s:rPr>
+      <s:t>ОП.06 Информационные технологии в профессиональной деятельности  Дерябкина Е.В. УЛК1,ауд.401</s:t>
+    </s:r>
+  </s:si>
+  <s:si>
+    <s:r>
+      <s:rPr>
+        <s:vertAlign val="baseline"/>
+        <s:scheme val="minor"/>
+      </s:rPr>
+      <s:t>ОП.06 Информационные технологии в профессиональной деятельности  Дерябкина Е.В. УЛК1,ауд.401</s:t>
+    </s:r>
+  </s:si>
+  <s:si>
+    <s:t>ОП.05 Сервисная деятельность Кузнецов А.В. УЛК1,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.03 Основы гегодезии и картографии Ляхов А.К. УЛК2,ауд.211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01Разработка проктной док. по организации строитльства объектов кап. строительства Чубцов К.В. УЛК1,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01 Организация и управление процессами подготовки геологических материалов и оборудования Гурулева Е.А. УЛК1,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.03 Безопсность жизнидеятельности Жевнеров В.В. УЛК1,ауд.104</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.02 Основы анализа бухгалтерской (финансовой) отчетности Шевцова В.А. УЛК1,ауд.109</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП. 07 Правовое обеспечение профессиональной деятельности Кузнецов А.В. УЛК1,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.02 Геодезическое обеспечение строительства Иванов Н.А. УЛК1,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗУ-Д62</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МД-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МЭО-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ПГ-Д62</s:t>
+  </s:si>
+  <s:si>
+    <s:t>РУПО-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>РУПО-Д62</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СЭЗ-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ТТО-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЭМС-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЭУ-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>сп.площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Гузеева Ф.П.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Масленников А.Е</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Куркова А.И.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1общ,ауд.35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Соловьева Т.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Князева П.Г.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Карамзина К.Н.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Стафеева Е.М.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Чернова К.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Орлова Е.Р.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Бикбаева Д.Д.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Ноздреватых У.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УПМ-105</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Иванов Н.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 14.09 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МСУ-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Стафеева Е.М. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 10 Основы безопасности и защита Родины Карнаухов В.В. УЛК2,ауд.304</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЭГС-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МЖО-Д41</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Стафеева</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Князева П..</s:t>
+  </s:si>
+  <s:si>
+    <s:t>общ1-35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Боженко И.И.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Соловьева Т.С.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>сп. площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 14.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01 Содержание, контроль и техническая эксплуатация жилищного фонда Цыганков М.Е.УЛК1,ауд.016</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 04.02 Основы анализа бухгалтерской (финансовой) отчетности Шевцова В.А. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 15.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.05 География Куркова А.И. Упм-207
+</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.05 География Куркова А.И. УПМ-207
+</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика Касьян Д.П., УЛК2,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.08 Основы проектирования баз данных Александрова Л.В. УЛК1,ауд.406</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.07 Экономика отрасли Шевцова В.А. УЛК1,ауд.109</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 01.01 Практические основы бухгалтерского учета активов организации и источников их формирования                         Ловыгина И.А. УЛК1,ауд.310 </s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.01 История России Отт А.А. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК
+  01.04 Документационное обеспечение кадровой службы  Фомина С.А. УЛК1,ауд.118</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.04 Документационное обеспечение кадровой службы  Фомина С.А. УЛК1,ауд.118</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.03 Определение кадастровой стоимости объектов недвижимости  Ноздреватых У.А. УЛК1,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.03 Иностранный язык в профессиональной деятельности Отт А.А, УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.05 Психология общения Куркова А.Н.  упм-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.05 Психология общения Куркова А.Н.  УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1 общ.-35</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Чернова </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 16.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МД-Д</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Елхова Г.А. 1общ.,ауд.35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 10 Основы безопасности и защита Родины Епифанцева Е.В. УЛК2,ауд.207</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.01 Русский  язык  Елхова Г.А. УЛК2,ауд.  </s:t>
+  </s:si>
+  <s:si>
+    <s:t>СЭЗ-Д62</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.01 История России Коскина Е.В. Общ.1-акт.зал</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ. 02 История Коскина Е.В. Общ.1-акт.зал</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.06 Маркшейдерско-геодезические приборы Иванов Н.А.. УЛК1,ауд.013</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.02 Прикладные компьютерные программы в прфессиональной деятельности Зинкевич Н.С. УЛК1,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Организация геологических работ и охрана труда Ащаулова Я.Н. УЛК1,ауд.409</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Проект производства работ Коплык В.Л.УЛК1,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 09.03 Обеспечение безопасности веб-приложений.  Насонова Н.А. УЛК1,ауд.402</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОПД.12 Технология поиска работы Онищенко Н.Н. УЛК1,ауд.112</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МЭОО-Д51</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЭМС--Д51</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК1,ауд.пг-д41</s:t>
+  </s:si>
 </s:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<s:styleSheet xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac x16r2">
+<s:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14ac x16r2">
   <s:numFmts count="5">
     <s:numFmt numFmtId="160" formatCode="dd/mmm"/>
     <s:numFmt numFmtId="161" formatCode="[$-F400]h:mm:ss"/>
@@ -9313,7 +10484,7 @@
     <s:numFmt numFmtId="165" formatCode="General"/>
     <s:numFmt numFmtId="166" formatCode="dd\.mm"/>
   </s:numFmts>
-  <s:fonts count="53">
+  <s:fonts count="60">
     <s:font>
       <s:name val="Liberation Sans"/>
       <s:color theme="1"/>
@@ -9598,6 +10769,42 @@
     </s:font>
     <s:font>
       <s:b val="0"/>
+      <s:sz val="14"/>
+    </s:font>
+    <s:font>
+      <s:name val="Times New Roman"/>
+      <s:b val="1"/>
+      <s:i val="1"/>
+      <s:color rgb="FFFF0000"/>
+      <s:sz val="18"/>
+    </s:font>
+    <s:font>
+      <s:name val="Times New Roman"/>
+      <s:sz val="18"/>
+    </s:font>
+    <s:font>
+      <s:name val="Arial"/>
+      <s:color rgb="FF000000"/>
+      <s:sz val="8"/>
+    </s:font>
+    <s:font>
+      <s:name val="Arial"/>
+      <s:color rgb="FF000000"/>
+      <s:sz val="12"/>
+    </s:font>
+    <s:font>
+      <s:name val="Times New Roman"/>
+      <s:color rgb="FF000000"/>
+      <s:sz val="12"/>
+    </s:font>
+    <s:font>
+      <s:name val="Times New Roman"/>
+      <s:b val="1"/>
+      <s:sz val="16"/>
+    </s:font>
+    <s:font>
+      <s:name val="Tinos"/>
+      <s:color rgb="FF000000"/>
       <s:sz val="14"/>
     </s:font>
   </s:fonts>
@@ -10493,7 +11700,7 @@
   <s:cellStyleXfs count="1">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </s:cellStyleXfs>
-  <s:cellXfs count="277">
+  <s:cellXfs count="295">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <s:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <s:alignment horizontal="left" mc:Ignorable="vyd"/>
@@ -11271,6 +12478,60 @@
       <s:alignment horizontal="center" mc:Ignorable="vyd"/>
     </s:xf>
     <s:xf fontId="50" borderId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="16" borderId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="36" borderId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="53" borderId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="28" borderId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="15" borderId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="54" borderId="82" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="left" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="161" fontId="29" fillId="2" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="left" vertical="center" wrapText="1" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="40" borderId="22" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="55" borderId="82" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="55" borderId="82" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="left" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="56" borderId="82" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="left" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="57" borderId="82" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="left" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="29" borderId="82" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="left" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="58" borderId="22" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="58" borderId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="26" borderId="22" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="9" borderId="82" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="59" borderId="22" applyFont="1" applyBorder="1" applyAlignment="1">
       <s:alignment horizontal="center" mc:Ignorable="vyd"/>
     </s:xf>
   </s:cellXfs>
@@ -11495,10 +12756,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <s:sheetFormatPr defaultColWidth="10" defaultRowHeight="12.75"/>
   <s:cols>
-    <s:col min="1" max="1" width="16.574" customWidth="1"/>
+    <s:col min="1" max="1" width="19.688" customWidth="1"/>
     <s:col min="2" max="2" width="14.852" customWidth="1"/>
     <s:col min="3" max="3" width="137.711" customWidth="1"/>
     <s:col min="4" max="4" width="40.852" customWidth="1"/>
@@ -11512,7 +12773,7 @@
         <s:v>0</s:v>
       </s:c>
       <s:c r="C1" s="2" t="s">
-        <s:v>2948</s:v>
+        <s:v>3325</s:v>
       </s:c>
       <s:c r="D1" s="2"/>
     </s:row>
@@ -11547,756 +12808,734 @@
       <s:c r="D4" s="99"/>
     </s:row>
     <s:row r="5" ht="25.5" customHeight="1">
-      <s:c r="A5" s="139" t="s">
-        <s:v>21</s:v>
-      </s:c>
-      <s:c r="B5" s="140" t="s">
-        <s:v>2855</s:v>
-      </s:c>
-      <s:c r="C5" s="139" t="s">
-        <s:v>2856</s:v>
-      </s:c>
-      <s:c r="D5" s="223" t="s">
-        <s:v>1343</s:v>
-      </s:c>
+      <s:c r="A5" s="139"/>
+      <s:c r="B5" s="140"/>
+      <s:c r="C5" s="139"/>
+      <s:c r="D5" s="223"/>
     </s:row>
     <s:row r="6" ht="25.5" customHeight="1">
-      <s:c r="A6" s="139" t="s">
-        <s:v>73</s:v>
-      </s:c>
-      <s:c r="B6" s="140" t="s">
-        <s:v>2855</s:v>
-      </s:c>
-      <s:c r="C6" s="139" t="s">
-        <s:v>2856</s:v>
-      </s:c>
-      <s:c r="D6" s="223" t="s">
-        <s:v>1343</s:v>
-      </s:c>
+      <s:c r="A6" s="99" t="s">
+        <s:v>831</s:v>
+      </s:c>
+      <s:c r="B6" s="100"/>
+      <s:c r="C6" s="100"/>
+      <s:c r="D6" s="175"/>
     </s:row>
-    <s:row r="7" ht="25.5" customHeight="1">
-      <s:c r="A7" s="139" t="s">
-        <s:v>62</s:v>
-      </s:c>
-      <s:c r="B7" s="140" t="s">
-        <s:v>1960</s:v>
-      </s:c>
-      <s:c r="C7" s="139" t="s">
-        <s:v>2934</s:v>
-      </s:c>
-      <s:c r="D7" s="223" t="s">
+    <s:row r="7" ht="36.375" customHeight="1">
+      <s:c r="A7" s="96" t="s">
+        <s:v>3270</s:v>
+      </s:c>
+      <s:c r="B7" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C7" s="174" t="s">
+        <s:v>3297</s:v>
+      </s:c>
+      <s:c r="D7" s="174"/>
+    </s:row>
+    <s:row r="8" ht="36.375" customHeight="1">
+      <s:c r="A8" s="96" t="s">
+        <s:v>3250</s:v>
+      </s:c>
+      <s:c r="B8" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C8" s="174" t="s">
+        <s:v>3327</s:v>
+      </s:c>
+      <s:c r="D8" s="174"/>
+    </s:row>
+    <s:row r="9" ht="36.375" customHeight="1">
+      <s:c r="A9" s="96" t="s">
+        <s:v>3250</s:v>
+      </s:c>
+      <s:c r="B9" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C9" s="174" t="s">
+        <s:v>51</s:v>
+      </s:c>
+      <s:c r="D9" s="174"/>
+    </s:row>
+    <s:row r="10" ht="36.375" customHeight="1">
+      <s:c r="A10" s="96" t="s">
+        <s:v>3252</s:v>
+      </s:c>
+      <s:c r="B10" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C10" s="174" t="s">
+        <s:v>3328</s:v>
+      </s:c>
+      <s:c r="D10" s="174"/>
+    </s:row>
+    <s:row r="11" ht="36.375" customHeight="1">
+      <s:c r="A11" s="96" t="s">
+        <s:v>3252</s:v>
+      </s:c>
+      <s:c r="B11" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C11" s="174" t="s">
+        <s:v>3327</s:v>
+      </s:c>
+      <s:c r="D11" s="174"/>
+    </s:row>
+    <s:row r="12" ht="36.375" customHeight="1">
+      <s:c r="A12" s="96" t="s">
+        <s:v>3330</s:v>
+      </s:c>
+      <s:c r="B12" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C12" s="174" t="s">
+        <s:v>2165</s:v>
+      </s:c>
+      <s:c r="D12" s="174"/>
+    </s:row>
+    <s:row r="13" ht="36.375" customHeight="1">
+      <s:c r="A13" s="96" t="s">
+        <s:v>3276</s:v>
+      </s:c>
+      <s:c r="B13" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C13" s="174" t="s">
+        <s:v>51</s:v>
+      </s:c>
+      <s:c r="D13" s="174"/>
+    </s:row>
+    <s:row r="14" ht="36.375" customHeight="1">
+      <s:c r="A14" s="96" t="s">
+        <s:v>38</s:v>
+      </s:c>
+      <s:c r="B14" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C14" s="174" t="s">
+        <s:v>1500</s:v>
+      </s:c>
+      <s:c r="D14" s="174"/>
+    </s:row>
+    <s:row r="15" ht="36.375" customHeight="1">
+      <s:c r="A15" s="96" t="s">
+        <s:v>38</s:v>
+      </s:c>
+      <s:c r="B15" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C15" s="174" t="s">
+        <s:v>3331</s:v>
+      </s:c>
+      <s:c r="D15" s="174"/>
+    </s:row>
+    <s:row r="16" ht="36.375" customHeight="1">
+      <s:c r="A16" s="96" t="s">
+        <s:v>101</s:v>
+      </s:c>
+      <s:c r="B16" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C16" s="174" t="s">
+        <s:v>3332</s:v>
+      </s:c>
+      <s:c r="D16" s="174"/>
+    </s:row>
+    <s:row r="17" ht="36.375" customHeight="1">
+      <s:c r="A17" s="96" t="s">
+        <s:v>39</s:v>
+      </s:c>
+      <s:c r="B17" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C17" s="174" t="s">
+        <s:v>3333</s:v>
+      </s:c>
+      <s:c r="D17" s="174"/>
+    </s:row>
+    <s:row r="18" ht="36.375" customHeight="1">
+      <s:c r="A18" s="96" t="s">
+        <s:v>109</s:v>
+      </s:c>
+      <s:c r="B18" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C18" s="174" t="s">
+        <s:v>3334</s:v>
+      </s:c>
+      <s:c r="D18" s="174"/>
+    </s:row>
+    <s:row r="19" ht="36.375" customHeight="1">
+      <s:c r="A19" s="96" t="s">
+        <s:v>218</s:v>
+      </s:c>
+      <s:c r="B19" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C19" s="174" t="s">
+        <s:v>3315</s:v>
+      </s:c>
+      <s:c r="D19" s="174"/>
+    </s:row>
+    <s:row r="20" ht="36.375" customHeight="1">
+      <s:c r="A20" s="96" t="s">
+        <s:v>112</s:v>
+      </s:c>
+      <s:c r="B20" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C20" s="174" t="s">
+        <s:v>51</s:v>
+      </s:c>
+      <s:c r="D20" s="174"/>
+    </s:row>
+    <s:row r="21" ht="36.375" customHeight="1">
+      <s:c r="A21" s="96" t="s">
+        <s:v>112</s:v>
+      </s:c>
+      <s:c r="B21" s="96">
+        <s:v>4</s:v>
+      </s:c>
+      <s:c r="C21" s="174" t="s">
+        <s:v>3335</s:v>
+      </s:c>
+      <s:c r="D21" s="174"/>
+    </s:row>
+    <s:row r="22" ht="36.375" customHeight="1">
+      <s:c r="A22" s="96" t="s">
+        <s:v>129</s:v>
+      </s:c>
+      <s:c r="B22" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C22" s="174" t="s">
+        <s:v>3336</s:v>
+      </s:c>
+      <s:c r="D22" s="174"/>
+    </s:row>
+    <s:row r="23" ht="36.375" customHeight="1">
+      <s:c r="A23" s="96" t="s">
+        <s:v>67</s:v>
+      </s:c>
+      <s:c r="B23" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C23" s="174" t="s">
+        <s:v>51</s:v>
+      </s:c>
+      <s:c r="D23" s="174"/>
+    </s:row>
+    <s:row r="24" ht="36.375" customHeight="1">
+      <s:c r="A24" s="96" t="s">
+        <s:v>21</s:v>
+      </s:c>
+      <s:c r="B24" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C24" s="174" t="s">
+        <s:v>3337</s:v>
+      </s:c>
+      <s:c r="D24" s="174"/>
+    </s:row>
+    <s:row r="25" ht="36.375" customHeight="1">
+      <s:c r="A25" s="96" t="s">
+        <s:v>75</s:v>
+      </s:c>
+      <s:c r="B25" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C25" s="174" t="s">
+        <s:v>3338</s:v>
+      </s:c>
+      <s:c r="D25" s="174"/>
+    </s:row>
+    <s:row r="26" ht="23.25" customHeight="1">
+      <s:c r="A26" s="99" t="s">
+        <s:v>391</s:v>
+      </s:c>
+      <s:c r="B26" s="100"/>
+      <s:c r="C26" s="100"/>
+      <s:c r="D26" s="99"/>
+    </s:row>
+    <s:row r="27" ht="27" customHeight="1">
+      <s:c r="A27" s="290" t="s">
+        <s:v>3295</s:v>
+      </s:c>
+      <s:c r="B27" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C27" s="292" t="s">
+        <s:v>226</s:v>
+      </s:c>
+      <s:c r="D27" s="45" t="s">
+        <s:v>3287</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="28" ht="27" customHeight="1">
+      <s:c r="A28" s="290" t="s">
+        <s:v>3271</s:v>
+      </s:c>
+      <s:c r="B28" s="291">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C28" s="292" t="s">
+        <s:v>901</s:v>
+      </s:c>
+      <s:c r="D28" s="45" t="s">
+        <s:v>3284</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="29" ht="27" customHeight="1">
+      <s:c r="A29" s="290" t="s">
+        <s:v>3249</s:v>
+      </s:c>
+      <s:c r="B29" s="291">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C29" s="292" t="s">
+        <s:v>226</s:v>
+      </s:c>
+      <s:c r="D29" s="45" t="s">
+        <s:v>3287</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="30" ht="27" customHeight="1">
+      <s:c r="A30" s="290" t="s">
+        <s:v>3250</s:v>
+      </s:c>
+      <s:c r="B30" s="291">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C30" s="292" t="s">
+        <s:v>1153</s:v>
+      </s:c>
+      <s:c r="D30" s="45" t="s">
+        <s:v>3285</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="31" ht="27" customHeight="1">
+      <s:c r="A31" s="290" t="s">
+        <s:v>3251</s:v>
+      </s:c>
+      <s:c r="B31" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C31" s="292" t="s">
+        <s:v>1153</s:v>
+      </s:c>
+      <s:c r="D31" s="45" t="s">
+        <s:v>3285</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="32" ht="27" customHeight="1">
+      <s:c r="A32" s="290" t="s">
+        <s:v>3273</s:v>
+      </s:c>
+      <s:c r="B32" s="291">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C32" s="292" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D32" s="45" t="s">
+        <s:v>94</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="33" ht="27" customHeight="1">
+      <s:c r="A33" s="290" t="s">
+        <s:v>3274</s:v>
+      </s:c>
+      <s:c r="B33" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C33" s="292" t="s">
+        <s:v>901</s:v>
+      </s:c>
+      <s:c r="D33" s="45" t="s">
+        <s:v>3284</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="34" ht="27" customHeight="1">
+      <s:c r="A34" s="290" t="s">
+        <s:v>3274</s:v>
+      </s:c>
+      <s:c r="B34" s="291">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C34" s="292" t="s">
+        <s:v>1153</s:v>
+      </s:c>
+      <s:c r="D34" s="45" t="s">
+        <s:v>3285</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="35" ht="27" customHeight="1">
+      <s:c r="A35" s="290" t="s">
+        <s:v>3252</s:v>
+      </s:c>
+      <s:c r="B35" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C35" s="292" t="s">
+        <s:v>1035</s:v>
+      </s:c>
+      <s:c r="D35" s="45" t="s">
+        <s:v>3280</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="36" ht="27" customHeight="1">
+      <s:c r="A36" s="290" t="s">
+        <s:v>3298</s:v>
+      </s:c>
+      <s:c r="B36" s="291">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C36" s="292" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D36" s="45" t="s">
+        <s:v>123</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="37" ht="27" customHeight="1">
+      <s:c r="A37" s="290" t="s">
+        <s:v>3254</s:v>
+      </s:c>
+      <s:c r="B37" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C37" s="292" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D37" s="45" t="s">
+        <s:v>94</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="38" ht="27" customHeight="1">
+      <s:c r="A38" s="290" t="s">
+        <s:v>95</s:v>
+      </s:c>
+      <s:c r="B38" s="291">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C38" s="292" t="s">
+        <s:v>1035</s:v>
+      </s:c>
+      <s:c r="D38" s="45" t="s">
+        <s:v>3280</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="39" ht="27" customHeight="1">
+      <s:c r="A39" s="290" t="s">
+        <s:v>95</s:v>
+      </s:c>
+      <s:c r="B39" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C39" s="292" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D39" s="45" t="s">
+        <s:v>123</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="40" ht="27" customHeight="1">
+      <s:c r="A40" s="290" t="s">
+        <s:v>104</s:v>
+      </s:c>
+      <s:c r="B40" s="291">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C40" s="292" t="s">
+        <s:v>1139</s:v>
+      </s:c>
+      <s:c r="D40" s="45" t="s">
+        <s:v>3289</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="41" ht="27" customHeight="1">
+      <s:c r="A41" s="290" t="s">
+        <s:v>109</s:v>
+      </s:c>
+      <s:c r="B41" s="291">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C41" s="292" t="s">
+        <s:v>752</s:v>
+      </s:c>
+      <s:c r="D41" s="45" t="s">
+        <s:v>663</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="42" ht="27" customHeight="1">
+      <s:c r="A42" s="290" t="s">
+        <s:v>110</s:v>
+      </s:c>
+      <s:c r="B42" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C42" s="292" t="s">
+        <s:v>113</s:v>
+      </s:c>
+      <s:c r="D42" s="45" t="s">
+        <s:v>114</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="43" ht="27" customHeight="1">
+      <s:c r="A43" s="290" t="s">
+        <s:v>111</s:v>
+      </s:c>
+      <s:c r="B43" s="291">
+        <s:v>2.3</s:v>
+      </s:c>
+      <s:c r="C43" s="292" t="s">
+        <s:v>352</s:v>
+      </s:c>
+      <s:c r="D43" s="45" t="s">
         <s:v>121</s:v>
       </s:c>
-    </s:row>
-    <s:row r="8" ht="25.5" customHeight="1">
-      <s:c r="A8" s="139" t="s">
-        <s:v>187</s:v>
-      </s:c>
-      <s:c r="B8" s="140" t="s">
-        <s:v>1960</s:v>
-      </s:c>
-      <s:c r="C8" s="139" t="s">
-        <s:v>2935</s:v>
-      </s:c>
-      <s:c r="D8" s="223" t="s">
-        <s:v>1962</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="9" ht="25.5" customHeight="1">
-      <s:c r="A9" s="139" t="s">
-        <s:v>80</s:v>
-      </s:c>
-      <s:c r="B9" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C9" s="139" t="s">
-        <s:v>2952</s:v>
-      </s:c>
-      <s:c r="D9" s="223" t="s">
-        <s:v>119</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="10" ht="25.5" customHeight="1">
-      <s:c r="A10" s="139" t="s">
-        <s:v>131</s:v>
-      </s:c>
-      <s:c r="B10" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C10" s="139" t="s">
-        <s:v>2952</s:v>
-      </s:c>
-      <s:c r="D10" s="223" t="s">
-        <s:v>2930</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="11" ht="25.5" customHeight="1">
-      <s:c r="A11" s="139" t="s">
-        <s:v>75</s:v>
-      </s:c>
-      <s:c r="B11" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C11" s="139" t="s">
-        <s:v>2759</s:v>
-      </s:c>
-      <s:c r="D11" s="273" t="s">
-        <s:v>1694</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="12" ht="27.75" customHeight="1">
-      <s:c r="A12" s="139" t="s">
-        <s:v>50</s:v>
-      </s:c>
-      <s:c r="B12" s="140" t="s">
-        <s:v>1713</s:v>
-      </s:c>
-      <s:c r="C12" s="139" t="s">
-        <s:v>2920</s:v>
-      </s:c>
-      <s:c r="D12" s="273" t="s">
-        <s:v>181</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="13" ht="27.75" customHeight="1">
-      <s:c r="A13" s="139" t="s">
-        <s:v>112</s:v>
-      </s:c>
-      <s:c r="B13" s="140" t="s">
-        <s:v>1960</s:v>
-      </s:c>
-      <s:c r="C13" s="139" t="s">
-        <s:v>2959</s:v>
-      </s:c>
-      <s:c r="D13" s="273" t="s">
-        <s:v>1712</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="14" ht="27.75" customHeight="1">
-      <s:c r="A14" s="139" t="s">
-        <s:v>237</s:v>
-      </s:c>
-      <s:c r="B14" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C14" s="139" t="s">
-        <s:v>2949</s:v>
-      </s:c>
-      <s:c r="D14" s="273" t="s">
-        <s:v>2951</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="15" ht="27.75" customHeight="1">
-      <s:c r="A15" s="139" t="s">
-        <s:v>57</s:v>
-      </s:c>
-      <s:c r="B15" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C15" s="139" t="s">
-        <s:v>2950</s:v>
-      </s:c>
-      <s:c r="D15" s="273" t="s">
-        <s:v>119</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="16" ht="27.75" customHeight="1">
-      <s:c r="A16" s="139" t="s">
-        <s:v>78</s:v>
-      </s:c>
-      <s:c r="B16" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C16" s="139" t="s">
-        <s:v>2648</s:v>
-      </s:c>
-      <s:c r="D16" s="141" t="s">
-        <s:v>2649</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="17" ht="27.75" customHeight="1">
-      <s:c r="A17" s="139" t="s">
-        <s:v>60</s:v>
-      </s:c>
-      <s:c r="B17" s="140" t="s">
-        <s:v>1960</s:v>
-      </s:c>
-      <s:c r="C17" s="139" t="s">
-        <s:v>2880</s:v>
-      </s:c>
-      <s:c r="D17" s="141" t="s">
-        <s:v>783</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="18" ht="27.75" customHeight="1">
-      <s:c r="A18" s="139" t="s">
-        <s:v>128</s:v>
-      </s:c>
-      <s:c r="B18" s="140" t="s">
-        <s:v>2813</s:v>
-      </s:c>
-      <s:c r="C18" s="139" t="s">
-        <s:v>2814</s:v>
-      </s:c>
-      <s:c r="D18" s="141" t="s">
-        <s:v>784</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="19" ht="27.75" customHeight="1">
-      <s:c r="A19" s="139" t="s">
-        <s:v>130</s:v>
-      </s:c>
-      <s:c r="B19" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C19" s="224" t="s">
-        <s:v>2937</s:v>
-      </s:c>
-      <s:c r="D19" s="141" t="s">
-        <s:v>783</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="20" ht="30" customHeight="1">
-      <s:c r="A20" s="139" t="s">
-        <s:v>25</s:v>
-      </s:c>
-      <s:c r="B20" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C20" s="139" t="s">
-        <s:v>2937</s:v>
-      </s:c>
-      <s:c r="D20" s="141" t="s">
-        <s:v>394</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="21" ht="25.5" customHeight="1">
-      <s:c r="A21" s="139" t="s">
-        <s:v>52</s:v>
-      </s:c>
-      <s:c r="B21" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C21" s="139" t="s">
-        <s:v>2950</s:v>
-      </s:c>
-      <s:c r="D21" s="240" t="s">
-        <s:v>1957</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="22" ht="25.5" customHeight="1">
-      <s:c r="A22" s="139" t="s">
-        <s:v>160</s:v>
-      </s:c>
-      <s:c r="B22" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C22" s="139" t="s">
-        <s:v>2950</s:v>
-      </s:c>
-      <s:c r="D22" s="240" t="s">
-        <s:v>824</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="23" ht="25.5" customHeight="1">
-      <s:c r="A23" s="139" t="s">
-        <s:v>71</s:v>
-      </s:c>
-      <s:c r="B23" s="140" t="s">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C23" s="139" t="s">
-        <s:v>2783</s:v>
-      </s:c>
-      <s:c r="D23" s="240" t="s">
-        <s:v>2784</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="24" ht="25.5" customHeight="1">
-      <s:c r="A24" s="139" t="s">
-        <s:v>67</s:v>
-      </s:c>
-      <s:c r="B24" s="140" t="s">
-        <s:v>1854</s:v>
-      </s:c>
-      <s:c r="C24" s="139" t="s">
-        <s:v>2960</s:v>
-      </s:c>
-      <s:c r="D24" s="240" t="s">
-        <s:v>1172</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="25" ht="25.5" customHeight="1">
-      <s:c r="A25" s="99" t="s">
-        <s:v>831</s:v>
-      </s:c>
-      <s:c r="B25" s="100"/>
-      <s:c r="C25" s="100"/>
-      <s:c r="D25" s="175"/>
-    </s:row>
-    <s:row r="26" ht="31.5" customHeight="1">
-      <s:c r="A26" s="96" t="s">
-        <s:v>38</s:v>
-      </s:c>
-      <s:c r="B26" s="164">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C26" s="162" t="s">
-        <s:v>2764</s:v>
-      </s:c>
-      <s:c r="D26" s="174"/>
-    </s:row>
-    <s:row r="27" ht="31.5" customHeight="1">
-      <s:c r="A27" s="96" t="s">
-        <s:v>95</s:v>
-      </s:c>
-      <s:c r="B27" s="164">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C27" s="162" t="s">
-        <s:v>2953</s:v>
-      </s:c>
-      <s:c r="D27" s="174"/>
-    </s:row>
-    <s:row r="28" ht="31.5" customHeight="1">
-      <s:c r="A28" s="96" t="s">
-        <s:v>127</s:v>
-      </s:c>
-      <s:c r="B28" s="164">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C28" s="162" t="s">
-        <s:v>2333</s:v>
-      </s:c>
-      <s:c r="D28" s="174"/>
-    </s:row>
-    <s:row r="29" ht="31.5" customHeight="1">
-      <s:c r="A29" s="96" t="s">
-        <s:v>127</s:v>
-      </s:c>
-      <s:c r="B29" s="164">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C29" s="162" t="s">
-        <s:v>2764</s:v>
-      </s:c>
-      <s:c r="D29" s="174"/>
-    </s:row>
-    <s:row r="30" ht="31.5" customHeight="1">
-      <s:c r="A30" s="96" t="s">
-        <s:v>101</s:v>
-      </s:c>
-      <s:c r="B30" s="164">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C30" s="162" t="s">
-        <s:v>2764</s:v>
-      </s:c>
-      <s:c r="D30" s="174"/>
-    </s:row>
-    <s:row r="31" ht="31.5" customHeight="1">
-      <s:c r="A31" s="96" t="s">
-        <s:v>104</s:v>
-      </s:c>
-      <s:c r="B31" s="164">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C31" s="162" t="s">
-        <s:v>2965</s:v>
-      </s:c>
-      <s:c r="D31" s="174"/>
-    </s:row>
-    <s:row r="32" ht="31.5" customHeight="1">
-      <s:c r="A32" s="96" t="s">
-        <s:v>110</s:v>
-      </s:c>
-      <s:c r="B32" s="164">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C32" s="162" t="s">
-        <s:v>2368</s:v>
-      </s:c>
-      <s:c r="D32" s="174"/>
-    </s:row>
-    <s:row r="33" ht="31.5" customHeight="1">
-      <s:c r="A33" s="96" t="s">
-        <s:v>111</s:v>
-      </s:c>
-      <s:c r="B33" s="164">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C33" s="162" t="s">
-        <s:v>1395</s:v>
-      </s:c>
-      <s:c r="D33" s="174"/>
-    </s:row>
-    <s:row r="34" ht="31.5" customHeight="1">
-      <s:c r="A34" s="96" t="s">
-        <s:v>43</s:v>
-      </s:c>
-      <s:c r="B34" s="164">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C34" s="162" t="s">
-        <s:v>1609</s:v>
-      </s:c>
-      <s:c r="D34" s="174"/>
-    </s:row>
-    <s:row r="35" ht="31.5" customHeight="1">
-      <s:c r="A35" s="96" t="s">
-        <s:v>46</s:v>
-      </s:c>
-      <s:c r="B35" s="164">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C35" s="162" t="s">
-        <s:v>2954</s:v>
-      </s:c>
-      <s:c r="D35" s="174"/>
-    </s:row>
-    <s:row r="36" ht="31.5" customHeight="1">
-      <s:c r="A36" s="96" t="s">
-        <s:v>48</s:v>
-      </s:c>
-      <s:c r="B36" s="164">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C36" s="162" t="s">
-        <s:v>51</s:v>
-      </s:c>
-      <s:c r="D36" s="174"/>
-    </s:row>
-    <s:row r="37" ht="31.5" customHeight="1">
-      <s:c r="A37" s="96" t="s">
-        <s:v>48</s:v>
-      </s:c>
-      <s:c r="B37" s="164">
-        <s:v>4</s:v>
-      </s:c>
-      <s:c r="C37" s="162" t="s">
-        <s:v>2954</s:v>
-      </s:c>
-      <s:c r="D37" s="174"/>
-    </s:row>
-    <s:row r="38" ht="31.5" customHeight="1">
-      <s:c r="A38" s="96" t="s">
-        <s:v>159</s:v>
-      </s:c>
-      <s:c r="B38" s="164">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C38" s="162" t="s">
-        <s:v>1395</s:v>
-      </s:c>
-      <s:c r="D38" s="174"/>
-    </s:row>
-    <s:row r="39" ht="31.5" customHeight="1">
-      <s:c r="A39" s="96" t="s">
-        <s:v>286</s:v>
-      </s:c>
-      <s:c r="B39" s="164">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C39" s="162" t="s">
-        <s:v>1395</s:v>
-      </s:c>
-      <s:c r="D39" s="174"/>
-    </s:row>
-    <s:row r="40" ht="31.5" customHeight="1">
-      <s:c r="A40" s="96" t="s">
-        <s:v>66</s:v>
-      </s:c>
-      <s:c r="B40" s="164">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C40" s="162" t="s">
-        <s:v>51</s:v>
-      </s:c>
-      <s:c r="D40" s="174"/>
-    </s:row>
-    <s:row r="41" ht="31.5" customHeight="1">
-      <s:c r="A41" s="96" t="s">
-        <s:v>66</s:v>
-      </s:c>
-      <s:c r="B41" s="164">
-        <s:v>4</s:v>
-      </s:c>
-      <s:c r="C41" s="162" t="s">
-        <s:v>2955</s:v>
-      </s:c>
-      <s:c r="D41" s="174"/>
-    </s:row>
-    <s:row r="42" ht="31.5" customHeight="1">
-      <s:c r="A42" s="96" t="s">
-        <s:v>18</s:v>
-      </s:c>
-      <s:c r="B42" s="164">
-        <s:v>1.2</s:v>
-      </s:c>
-      <s:c r="C42" s="162" t="s">
-        <s:v>1371</s:v>
-      </s:c>
-      <s:c r="D42" s="174"/>
-    </s:row>
-    <s:row r="43" ht="23.25" customHeight="1">
-      <s:c r="A43" s="99" t="s">
-        <s:v>391</s:v>
-      </s:c>
-      <s:c r="B43" s="100"/>
-      <s:c r="C43" s="100"/>
-      <s:c r="D43" s="99"/>
     </s:row>
     <s:row r="44" ht="27" customHeight="1">
-      <s:c r="A44" s="251" t="s">
-        <s:v>38</s:v>
-      </s:c>
-      <s:c r="B44" s="251">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C44" s="264" t="s">
-        <s:v>2246</s:v>
+      <s:c r="A44" s="290" t="s">
+        <s:v>41</s:v>
+      </s:c>
+      <s:c r="B44" s="291">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C44" s="292" t="s">
+        <s:v>113</s:v>
       </s:c>
       <s:c r="D44" s="45" t="s">
-        <s:v>103</s:v>
+        <s:v>114</s:v>
       </s:c>
     </s:row>
     <s:row r="45" ht="27" customHeight="1">
-      <s:c r="A45" s="251" t="s">
-        <s:v>95</s:v>
-      </s:c>
-      <s:c r="B45" s="251">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C45" s="274" t="s">
-        <s:v>2246</s:v>
+      <s:c r="A45" s="290" t="s">
+        <s:v>43</s:v>
+      </s:c>
+      <s:c r="B45" s="291">
+        <s:v>2.3</s:v>
+      </s:c>
+      <s:c r="C45" s="292" t="s">
+        <s:v>386</s:v>
       </s:c>
       <s:c r="D45" s="45" t="s">
-        <s:v>96</s:v>
+        <s:v>3290</s:v>
       </s:c>
     </s:row>
     <s:row r="46" ht="27" customHeight="1">
-      <s:c r="A46" s="251" t="s">
-        <s:v>101</s:v>
-      </s:c>
-      <s:c r="B46" s="251">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C46" s="264" t="s">
-        <s:v>259</s:v>
+      <s:c r="A46" s="290" t="s">
+        <s:v>48</s:v>
+      </s:c>
+      <s:c r="B46" s="291">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C46" s="292" t="s">
+        <s:v>1035</s:v>
       </s:c>
       <s:c r="D46" s="45" t="s">
-        <s:v>736</s:v>
+        <s:v>3280</s:v>
       </s:c>
     </s:row>
     <s:row r="47" ht="27" customHeight="1">
-      <s:c r="A47" s="251" t="s">
-        <s:v>104</s:v>
-      </s:c>
-      <s:c r="B47" s="251">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C47" s="264" t="s">
-        <s:v>821</s:v>
+      <s:c r="A47" s="290" t="s">
+        <s:v>3340</s:v>
+      </s:c>
+      <s:c r="B47" s="291">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C47" s="292" t="s">
+        <s:v>229</s:v>
       </s:c>
       <s:c r="D47" s="45" t="s">
-        <s:v>106</s:v>
+        <s:v>224</s:v>
       </s:c>
     </s:row>
     <s:row r="48" ht="27" customHeight="1">
-      <s:c r="A48" s="251" t="s">
-        <s:v>104</s:v>
-      </s:c>
-      <s:c r="B48" s="251">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C48" s="264" t="s">
-        <s:v>93</s:v>
+      <s:c r="A48" s="290" t="s">
+        <s:v>218</s:v>
+      </s:c>
+      <s:c r="B48" s="291">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C48" s="292" t="s">
+        <s:v>2583</s:v>
       </s:c>
       <s:c r="D48" s="45" t="s">
-        <s:v>164</s:v>
+        <s:v>123</s:v>
       </s:c>
     </s:row>
     <s:row r="49" ht="27" customHeight="1">
-      <s:c r="A49" s="251" t="s">
-        <s:v>109</s:v>
-      </s:c>
-      <s:c r="B49" s="251">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C49" s="264" t="s">
-        <s:v>821</s:v>
+      <s:c r="A49" s="290" t="s">
+        <s:v>112</s:v>
+      </s:c>
+      <s:c r="B49" s="291">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C49" s="292" t="s">
+        <s:v>2583</s:v>
       </s:c>
       <s:c r="D49" s="45" t="s">
-        <s:v>106</s:v>
+        <s:v>3286</s:v>
       </s:c>
     </s:row>
     <s:row r="50" ht="27" customHeight="1">
-      <s:c r="A50" s="251" t="s">
-        <s:v>109</s:v>
-      </s:c>
-      <s:c r="B50" s="251">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C50" s="274" t="s">
-        <s:v>2246</s:v>
+      <s:c r="A50" s="290" t="s">
+        <s:v>52</s:v>
+      </s:c>
+      <s:c r="B50" s="291">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C50" s="292" t="s">
+        <s:v>352</s:v>
       </s:c>
       <s:c r="D50" s="45" t="s">
-        <s:v>96</s:v>
+        <s:v>121</s:v>
       </s:c>
     </s:row>
     <s:row r="51" ht="27" customHeight="1">
-      <s:c r="A51" s="251" t="s">
-        <s:v>111</s:v>
-      </s:c>
-      <s:c r="B51" s="251">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C51" s="264" t="s">
-        <s:v>2246</s:v>
+      <s:c r="A51" s="290" t="s">
+        <s:v>55</s:v>
+      </s:c>
+      <s:c r="B51" s="291">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C51" s="292" t="s">
+        <s:v>1139</s:v>
       </s:c>
       <s:c r="D51" s="45" t="s">
-        <s:v>2961</s:v>
+        <s:v>3289</s:v>
       </s:c>
     </s:row>
     <s:row r="52" ht="27" customHeight="1">
-      <s:c r="A52" s="251" t="s">
-        <s:v>41</s:v>
-      </s:c>
-      <s:c r="B52" s="251">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C52" s="264" t="s">
-        <s:v>2246</s:v>
+      <s:c r="A52" s="290" t="s">
+        <s:v>55</s:v>
+      </s:c>
+      <s:c r="B52" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C52" s="292" t="s">
+        <s:v>905</s:v>
       </s:c>
       <s:c r="D52" s="45" t="s">
-        <s:v>96</s:v>
+        <s:v>3289</s:v>
       </s:c>
     </s:row>
     <s:row r="53" ht="27" customHeight="1">
-      <s:c r="A53" s="251" t="s">
-        <s:v>41</s:v>
-      </s:c>
-      <s:c r="B53" s="251">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C53" s="264" t="s">
-        <s:v>259</s:v>
+      <s:c r="A53" s="290" t="s">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="B53" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C53" s="292" t="s">
+        <s:v>229</s:v>
       </s:c>
       <s:c r="D53" s="45" t="s">
-        <s:v>736</s:v>
+        <s:v>224</s:v>
       </s:c>
     </s:row>
     <s:row r="54" ht="27" customHeight="1">
-      <s:c r="A54" s="251" t="s">
-        <s:v>218</s:v>
-      </s:c>
-      <s:c r="B54" s="251">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C54" s="264" t="s">
-        <s:v>900</s:v>
+      <s:c r="A54" s="290" t="s">
+        <s:v>62</s:v>
+      </s:c>
+      <s:c r="B54" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C54" s="292" t="s">
+        <s:v>2583</s:v>
       </s:c>
       <s:c r="D54" s="45" t="s">
-        <s:v>1341</s:v>
+        <s:v>3286</s:v>
       </s:c>
     </s:row>
     <s:row r="55" ht="27" customHeight="1">
-      <s:c r="A55" s="251" t="s">
-        <s:v>218</s:v>
-      </s:c>
-      <s:c r="B55" s="251">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C55" s="264" t="s">
-        <s:v>2246</s:v>
+      <s:c r="A55" s="290" t="s">
+        <s:v>187</s:v>
+      </s:c>
+      <s:c r="B55" s="291">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C55" s="292" t="s">
+        <s:v>386</s:v>
       </s:c>
       <s:c r="D55" s="45" t="s">
-        <s:v>123</s:v>
+        <s:v>3290</s:v>
       </s:c>
     </s:row>
     <s:row r="56" ht="27" customHeight="1">
-      <s:c r="A56" s="251" t="s">
-        <s:v>159</s:v>
-      </s:c>
-      <s:c r="B56" s="251">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C56" s="264" t="s">
-        <s:v>259</s:v>
+      <s:c r="A56" s="290" t="s">
+        <s:v>78</s:v>
+      </s:c>
+      <s:c r="B56" s="291">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C56" s="292" t="s">
+        <s:v>2583</s:v>
       </s:c>
       <s:c r="D56" s="45" t="s">
-        <s:v>736</s:v>
+        <s:v>94</s:v>
       </s:c>
     </s:row>
     <s:row r="57" ht="27" customHeight="1">
-      <s:c r="A57" s="251" t="s">
-        <s:v>115</s:v>
-      </s:c>
-      <s:c r="B57" s="251">
-        <s:v>1.3</s:v>
-      </s:c>
-      <s:c r="C57" s="264" t="s">
-        <s:v>172</s:v>
+      <s:c r="A57" s="290" t="s">
+        <s:v>78</s:v>
+      </s:c>
+      <s:c r="B57" s="291">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C57" s="292" t="s">
+        <s:v>117</s:v>
       </s:c>
       <s:c r="D57" s="45" t="s">
-        <s:v>823</s:v>
+        <s:v>825</s:v>
       </s:c>
     </s:row>
     <s:row r="58" ht="27" customHeight="1">
-      <s:c r="A58" s="251" t="s">
-        <s:v>129</s:v>
-      </s:c>
-      <s:c r="B58" s="251">
+      <s:c r="A58" s="290" t="s">
+        <s:v>78</s:v>
+      </s:c>
+      <s:c r="B58" s="291">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C58" s="264" t="s">
-        <s:v>979</s:v>
+      <s:c r="C58" s="292" t="s">
+        <s:v>229</s:v>
       </s:c>
       <s:c r="D58" s="45" t="s">
-        <s:v>1633</s:v>
+        <s:v>224</s:v>
       </s:c>
     </s:row>
     <s:row r="59" ht="27" customHeight="1">
-      <s:c r="A59" s="251" t="s">
-        <s:v>64</s:v>
-      </s:c>
-      <s:c r="B59" s="251">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C59" s="264" t="s">
-        <s:v>819</s:v>
+      <s:c r="A59" s="290" t="s">
+        <s:v>131</s:v>
+      </s:c>
+      <s:c r="B59" s="291">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C59" s="292" t="s">
+        <s:v>2583</s:v>
       </s:c>
       <s:c r="D59" s="45" t="s">
-        <s:v>955</s:v>
+        <s:v>3286</s:v>
       </s:c>
     </s:row>
     <s:row r="60" ht="27" customHeight="1">
-      <s:c r="A60" s="251" t="s">
-        <s:v>64</s:v>
-      </s:c>
-      <s:c r="B60" s="251">
+      <s:c r="A60" s="290" t="s">
+        <s:v>18</s:v>
+      </s:c>
+      <s:c r="B60" s="291">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C60" s="264" t="s">
-        <s:v>462</s:v>
+      <s:c r="C60" s="292" t="s">
+        <s:v>2583</s:v>
       </s:c>
       <s:c r="D60" s="45" t="s">
-        <s:v>256</s:v>
+        <s:v>96</s:v>
       </s:c>
     </s:row>
     <s:row r="61" ht="27" customHeight="1">
-      <s:c r="A61" s="251" t="s">
-        <s:v>66</s:v>
-      </s:c>
-      <s:c r="B61" s="251">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C61" s="264" t="s">
-        <s:v>819</s:v>
-      </s:c>
-      <s:c r="D61" s="45" t="s">
-        <s:v>955</s:v>
-      </s:c>
+      <s:c r="B61"/>
+      <s:c r="D61" s="35"/>
     </s:row>
     <s:row r="62" ht="27" customHeight="1">
       <s:c r="D62" s="35"/>
@@ -12304,51 +13543,32 @@
     <s:row r="63" ht="27" customHeight="1">
       <s:c r="D63" s="35"/>
     </s:row>
-    <s:row r="64" ht="27" customHeight="1">
+    <s:row r="64" ht="21.75" customHeight="1">
       <s:c r="D64" s="35"/>
     </s:row>
-    <s:row r="65" ht="27" customHeight="1">
+    <s:row r="65" ht="21" customHeight="1">
       <s:c r="D65" s="35"/>
     </s:row>
-    <s:row r="66" ht="27" customHeight="1">
-      <s:c r="D66" s="35"/>
-    </s:row>
-    <s:row r="67" ht="27" customHeight="1">
-      <s:c r="D67" s="35"/>
-    </s:row>
-    <s:row r="68" ht="27" customHeight="1">
-      <s:c r="D68" s="35"/>
-    </s:row>
-    <s:row r="69" ht="27" customHeight="1">
-      <s:c r="D69" s="35"/>
-    </s:row>
-    <s:row r="70" ht="21.75" customHeight="1">
-      <s:c r="D70" s="35"/>
-    </s:row>
-    <s:row r="71" ht="21" customHeight="1">
-      <s:c r="D71" s="35"/>
-    </s:row>
-    <s:row r="72" ht="17.25"/>
-    <s:row r="73" ht="17.25"/>
-    <s:row r="74" ht="17.25"/>
-    <s:row r="75" ht="17.25"/>
-    <s:row r="76" ht="17.25"/>
-    <s:row r="77" ht="17.25"/>
-    <s:row r="78" ht="17.25"/>
-    <s:row r="79" ht="17.25"/>
-    <s:row r="80" ht="17.25"/>
-    <s:row r="81" ht="17.25"/>
-    <s:row r="82" ht="17.25"/>
+    <s:row r="67" ht="13.5"/>
+    <s:row r="68" ht="13.5"/>
+    <s:row r="69" ht="13.5"/>
+    <s:row r="70" ht="13.5"/>
+    <s:row r="71" ht="13.5"/>
+    <s:row r="72" ht="13.5"/>
+    <s:row r="73" ht="13.5"/>
+    <s:row r="74" ht="13.5"/>
+    <s:row r="75" ht="13.5"/>
+    <s:row r="76" ht="13.5"/>
   </s:sheetData>
-  <s:autoFilter ref="A1:D71">
+  <s:autoFilter ref="A1:D65">
     <s:filterColumn colId="2" showButton="0"/>
   </s:autoFilter>
   <s:mergeCells count="5">
     <s:mergeCell ref="C1:D1"/>
     <s:mergeCell ref="A2:D2"/>
     <s:mergeCell ref="A4:D4"/>
-    <s:mergeCell ref="A25:D25"/>
-    <s:mergeCell ref="A43:D43"/>
+    <s:mergeCell ref="A6:D6"/>
+    <s:mergeCell ref="A26:D26"/>
   </s:mergeCells>
   <s:printOptions headings="0" gridLines="0"/>
   <s:pageMargins left="0.701" right="0.701" top="0.752" bottom="0.752" header="0.3" footer="0.3"/>

--- a/runtime/downloaded/Новая таблица (25).xlsx
+++ b/runtime/downloaded/Новая таблица (25).xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr/>
   <s:bookViews>
     <s:workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
@@ -9,7 +9,7 @@
     <s:sheet name="замена" sheetId="1" state="visible" r:id="rId1"/>
   </s:sheets>
   <s:definedNames>
-    <s:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">замена!$A$1:$D$77</s:definedName>
+    <s:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">замена!$A$1:$D$75</s:definedName>
     <s:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">замена!$A$1:$D$76</s:definedName>
     <s:definedName name="Диапазон_2">#REF!</s:definedName>
   </s:definedNames>
@@ -10472,11 +10472,445 @@
   <s:si>
     <s:t>УЛК1,ауд.пг-д41</s:t>
   </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 17.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗУ-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.  09 Физическая культураСтадник А.П. спорт. площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.  09 Физическая культура Стадник А.П. спорт. площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01Русский  язык  Семенова О.В.  УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 04 Обществознание  Маркитан А.Л. УЛК2,ауд.210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Правовое регулирование отношений в землеустройстве, кадастре и градостроительстве Ноздреватых У.А. УЛК1,ауд.409</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.02 Иностранный язык в профессиональной деятельности Чабунина О.А. общ2,ауд.25</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.03 Методика и практика архивоведения Солдаткина О.А. Общ.1-12</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.03 Иностранный язык в профессиональной деятельности Чабунина О.А. общ2,ауд.25</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 08.02 Графический дизайн и мультимедиа Савченко А.И. УЛК1,ауд.407       </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОСГЭ.04 Физическая культура  Севостьянова Ю.Б. спорт. площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.03 Инженерно-геодезические работы при строительстве зданий и инженерных сооружений Кириллов А.Б. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МД--Д31</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1общ-35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Зинкевич Н.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Учет выемки полезного ископаемого из недр       Лешкевич О.П. УПМ-10</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 18.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА .09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 19.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 20.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика, Соловьева Т.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 11 Физика Князева П.Г. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 07 Математика Гузеева Ф.П</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Практические основы бухгалтерского учета активов организации и источников их формирования                         Ловыгина И.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 09.01 Проектирование и разработка веб-приложений Александрова Л.В</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Учет выемки полезного ископаемого из недр     Лешкевич О.П.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.03 Безопсность жизнидеятельности Жевнеров В.В</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 08.01 Проектирование и разработка интерфейсов пользователя Насонова Н.А. УЛК1,ауд.402</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОПД.12 Технология поиска работы Онищенко Н.Н</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 08.01 Проектирование и разработка интерфейсов пользователя Насонова Н.А. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Топографо – геодезические изыскания Попович А.Н</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.03 Наладка электрооборудования      Сапожников В.В.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Инженерные изыскания в строительстве Чернова К.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01 Организация и планирование строительного производства инженерных сооружений                                                            Чубцов К.В. УЛК1,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.06 Иностранный язык Толызенкова А.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.05 География Куркова А.И.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 12 Химия Коробкова М.Н.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Разработка объемно-планировочных и конструктивных решений различных объектов капитального строительства Чубцов К.В.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.02 Разработка кода информационных систем Орлова Е.Р.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ. 02 История Степанова С.С.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.04 Геология Гурулева Е.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Учет выемки полезного ископаемого из недр   Лешкевич О.П.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 21.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.06 Иностранный язык Отт А.А., УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Стафеева Е.М. улк2,АУД.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.11 Физика Елхов Н.А..УЛК2,ауд.305     </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Выполнение топографических съемок и оформление их результатов Чернова К.А.  УЛК1,ауд.414</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 05.02 Разработка кода информационных систем Касьян Д.П.  УЛК2,ауд.110  </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.04 Иностранный язык в профессиональной деятельности Чабунина О.А. общ2,ауд.25</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Управление автоматизированными системами вентиляции и кондиционирования воздуха Зинкевич Н.С. УЛК1,АУД.406</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Управление автоматизированными системами вентиляции и кондиционирования воздуха Зинкевич Н.С. УЛК1,ауд.406</s:t>
+  </s:si>
+  <s:si>
+    <s:t>общ1,ауд.35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>общ.1,ауд.35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Пу</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Гурулева Е.А,</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 21.09 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.03 Тестирование информационных систем
+ Александрова Л.В.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.03 Тестирование информационных систем Александрова Л.В.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Организация работ связанных с соблюдением санитарного содержания.. УЛК1,ауд.016</s:t>
+  </s:si>
+  <s:si>
+    <s:t>02.03 Накладка электрооборудования</s:t>
+  </s:si>
+  <s:si>
+    <s:t>02.03 Накладка электрооборудования Сапожников В.В.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>РУПО-63</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский язык Елхова Г.А. УЛК2,ауд.211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 22.09 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ГС-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 11 Физика Швецова Д.А. УЛК2,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Елхова Г.А. ОБЩ1,АУД.35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.02 История  Чаплыгина Н.А, УЛК2,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.12 Менеджмент в профессиональной деятельности Кузнецов А.В. УЛК1,ауд305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Топографо – геодезические изыскания Попович А.Н. УЛК1,ауд.017</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1общ-35ауд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Иванов Н.А,</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Обеспечение контроля, учета и регулирования бесперебойной поставки электрической энергии потребителям Трофимчук Д.П. УПМ-209</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.04 Электронные геодезические средства измерений Бикбаева Д.Д. УЛК1,ауд.315</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Организация работ связанных с соблюдением санитарного содержания общего
+  имущества Цыганков М.Е.УЛК1,ауд.016</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 23.09 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>uc-l61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Елхова Г.А. 1 ОБЩ.-35 АУД.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.02 Основы экономики, менеджмента и маркетинга Онищенко Н.Н.. УЛК1, ауд.112</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.01 Замерщик на топографо-геодезических и маркшейдерских работах Чернова К.А.  УЛК1,ауд.301</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.02 Разработка кода информационных систем Орлова Е.Р.  УЛК2,ауд.408</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.03 Техническая  механика Бурылев Т.Д. УПМ-207</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Управление деятельностью структурных подразделений при выполнении строительно-монтажных работ... .                    Петрова Т.Н. УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Управление деятельностью структурных подразделений при выполнении строительно-монтажных работ...  Петрова Т.Н. УЛК1,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 08.02 Графический дизайн и мультимедиа
+Савченко А.И. УЛК1,ауд.407</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОСГЭ.04 Физическая культура 
+Севостьянова Ю.Б.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОСГЭ.04 Физическая культура  Севостьянова Ю.Б. спорт.площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 08.02 Графический дизайн и мультимедиа Савченко А.И. УЛК1,ауд.407</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский язык Галицкова А.В. УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский язык Галицкова А.В. УЛК2,ауд.304</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 24.09 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика Соловьева Т.А.УЛК2,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 09 Физическая культура Стадник А.П. спорт.площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.01 Русский  язык  Елхова Г.А. УЛК2,ауд. 306        </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЕН.02 Дискретная математика с элементами математической логики Быкова С.В. УЛК2,ауд.303</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Государственные, муниципальные архивы и архивы организаций  Шевелева Т.С. УЛК1,ауд.118</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Учет выемки полезного ископаемого из недр  Лешкевич О.П. УПМ-105</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.04 Физическая культура Севостьянова Ю.Б.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.04 Физическая культура Севостьянова Ю.Б. спорт.площадка</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 08.01 Проектирование и разработка интерфейсов пользователя
+Насонова Н.А. УЛК1,ауд.402   </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Князева  А.И.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Боженко И.И. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>орлова</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 25.09 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>vce-l61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 История Боженко И.И. УЛК2,ауд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.01 Русский  язык  Елхова Г.А. УЛК2,ауд.     </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 История Боженко И.И. УЛК2,ауд.114</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.01 Русский  язык  Елхова Г.А. УЛК2,ауд. 310    </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Основы управления  персоналом  Солдаткина О.А.. Общ.1-12</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.02 Монтаж, наладка и эксплуатация электрических сетей
+Сапожников В.В. упм-105</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.02 Монтаж, наладка и эксплуатация электрических сетей Сапожников В.В. УПМ-105</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ДОУ-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК1,ауд.Попович А.Н.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>2общ-25 ауд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 26.09 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01Русский  язык  Галицкова А.В. УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Стафеева Е.М.  УЛК2,ауд.202А</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.06 Иностранный язык Толызенкова А.А. УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.06 Иностранный язык Толызенкова А.А. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.06 Иностранный язык Толызенкова А.А. УЛК2,ауд.202</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 04 Обществознание Чаплыгина Н.А. УЛК2,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Разработка объемно-планировочных и конструктивных решений различных объектов капитального строительства Чубцов К.В. УЛК1,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.05 Цифровые технологии в профессиональной деятельности Теличкина И.П. УЛК1,ауд.020</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.03 Основы гегодезии и картографии Попович А.Н. УЛК1,ауд.016</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Организация работы с электронными документами Фомина С.А. УЛК1,ауд.118</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01 Техническая оценка и инвентаризация объектов недвижимости Первых Т.П. УЛК1,ауд.312</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Учет выемки полезного ископаемого из недр       Лешкевич О.П. УПМ-105</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДД61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1общ.-ауд.35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 28.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Стафеева Е.М. УЛК2,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Елхова Г.А. 1ОБЩ-35АУД.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 06.01 Монтажник каркасно-обшивных конструкций Васянкина В.С. УПМ,ауд.11</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Выполнение топографических съемок и оформление их результатов Чернова К.А.  УЛК1,ауд.013</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.01 История России Степанова С.С. УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 08.02 Графический дизайн и мультимедиа Савченко А.И. УЛК1,ауд.407  </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.02 Инженерно-геодезические работы при проектировании зданий и инженерных сооружений
+Чернова К.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.02 Инженерно-геодезические работы при проектировании зданий и инженерных сооружений
+Чернова К.А. УЛК1,ауд.013</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СИС-Д3</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Уарамзина К.Н.</s:t>
+  </s:si>
 </s:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<s:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14ac x16r2">
+<s:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <s:numFmts count="5">
     <s:numFmt numFmtId="160" formatCode="dd/mmm"/>
     <s:numFmt numFmtId="161" formatCode="[$-F400]h:mm:ss"/>
@@ -10808,7 +11242,7 @@
       <s:sz val="14"/>
     </s:font>
   </s:fonts>
-  <s:fills count="8">
+  <s:fills count="10">
     <s:fill>
       <s:patternFill patternType="none"/>
     </s:fill>
@@ -10848,6 +11282,18 @@
     <s:fill>
       <s:patternFill patternType="solid">
         <s:fgColor rgb="FFFFFFFF"/>
+      </s:patternFill>
+    </s:fill>
+    <s:fill>
+      <s:patternFill patternType="solid">
+        <s:fgColor rgb="FFFF6964"/>
+        <s:bgColor rgb="FFFF6964"/>
+      </s:patternFill>
+    </s:fill>
+    <s:fill>
+      <s:patternFill patternType="solid">
+        <s:fgColor rgb="FFFFC062"/>
+        <s:bgColor rgb="FFFFC062"/>
       </s:patternFill>
     </s:fill>
   </s:fills>
@@ -11700,7 +12146,7 @@
   <s:cellStyleXfs count="1">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </s:cellStyleXfs>
-  <s:cellXfs count="295">
+  <s:cellXfs count="303">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <s:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <s:alignment horizontal="left" mc:Ignorable="vyd"/>
@@ -12533,6 +12979,30 @@
     </s:xf>
     <s:xf fontId="59" borderId="22" applyFont="1" applyBorder="1" applyAlignment="1">
       <s:alignment horizontal="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <s:alignment horizontal="center" wrapText="1" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <s:alignment horizontal="left" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <s:alignment horizontal="left" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <s:alignment horizontal="center" wrapText="1" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="161" fontId="9" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="161" fontId="9" borderId="82" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="161" fontId="59" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="161" fontId="59" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="left" vertical="center" wrapText="1" mc:Ignorable="vyd"/>
     </s:xf>
   </s:cellXfs>
   <s:cellStyles count="1">
@@ -12756,7 +13226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<s:worksheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <s:sheetFormatPr defaultColWidth="10" defaultRowHeight="12.75"/>
   <s:cols>
     <s:col min="1" max="1" width="19.688" customWidth="1"/>
@@ -12765,99 +13235,103 @@
     <s:col min="4" max="4" width="40.852" customWidth="1"/>
   </s:cols>
   <s:sheetData>
-    <s:row r="1" ht="30.75" customHeight="1">
-      <s:c r="A1" s="1" t="s">
+    <s:row r="1" ht="27" customHeight="1">
+      <s:c r="A1" s="297" t="s">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="B1" s="1" t="s">
+      <s:c r="B1" s="297" t="s">
         <s:v>0</s:v>
       </s:c>
-      <s:c r="C1" s="2" t="s">
-        <s:v>3325</s:v>
-      </s:c>
-      <s:c r="D1" s="2"/>
+      <s:c r="C1" s="298" t="s">
+        <s:v>3473</s:v>
+      </s:c>
+      <s:c r="D1" s="298"/>
     </s:row>
-    <s:row r="2" ht="22.5" customHeight="1">
-      <s:c r="A2" s="134" t="s">
+    <s:row r="2" ht="27" customHeight="1">
+      <s:c r="A2" s="137" t="s">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="B2" s="137" t="s">
+        <s:v>4</s:v>
+      </s:c>
+      <s:c r="C2" s="137" t="s">
+        <s:v>5</s:v>
+      </s:c>
+      <s:c r="D2" s="138" t="s">
+        <s:v>0</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="3" ht="27" customHeight="1">
+      <s:c r="A3" s="99" t="s">
+        <s:v>6</s:v>
+      </s:c>
+      <s:c r="B3" s="99"/>
+      <s:c r="C3" s="99"/>
+      <s:c r="D3" s="99"/>
+    </s:row>
+    <s:row r="4" ht="27" customHeight="1">
+      <s:c r="A4" s="139"/>
+      <s:c r="B4" s="140"/>
+      <s:c r="C4" s="139"/>
+      <s:c r="D4" s="223"/>
+    </s:row>
+    <s:row r="5" ht="27" customHeight="1">
+      <s:c r="A5" s="99" t="s">
+        <s:v>831</s:v>
+      </s:c>
+      <s:c r="B5" s="100"/>
+      <s:c r="C5" s="100"/>
+      <s:c r="D5" s="175"/>
+    </s:row>
+    <s:row r="6" ht="31.688" customHeight="1">
+      <s:c r="A6" s="96" t="s">
+        <s:v>3295</s:v>
+      </s:c>
+      <s:c r="B6" s="96">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="B2" s="135"/>
-      <s:c r="C2" s="135"/>
-      <s:c r="D2" s="136"/>
+      <s:c r="C6" s="174" t="s">
+        <s:v>3474</s:v>
+      </s:c>
+      <s:c r="D6" s="174"/>
     </s:row>
-    <s:row r="3" ht="23.25" customHeight="1">
-      <s:c r="A3" s="137" t="s">
+    <s:row r="7" ht="32.625" customHeight="1">
+      <s:c r="A7" s="96" t="s">
+        <s:v>3295</s:v>
+      </s:c>
+      <s:c r="B7" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="B3" s="137" t="s">
-        <s:v>4</s:v>
-      </s:c>
-      <s:c r="C3" s="137" t="s">
-        <s:v>5</s:v>
-      </s:c>
-      <s:c r="D3" s="138" t="s">
-        <s:v>0</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="4" ht="25.5" customHeight="1">
-      <s:c r="A4" s="99" t="s">
-        <s:v>6</s:v>
-      </s:c>
-      <s:c r="B4" s="99"/>
-      <s:c r="C4" s="99"/>
-      <s:c r="D4" s="99"/>
-    </s:row>
-    <s:row r="5" ht="25.5" customHeight="1">
-      <s:c r="A5" s="139"/>
-      <s:c r="B5" s="140"/>
-      <s:c r="C5" s="139"/>
-      <s:c r="D5" s="223"/>
-    </s:row>
-    <s:row r="6" ht="25.5" customHeight="1">
-      <s:c r="A6" s="99" t="s">
-        <s:v>831</s:v>
-      </s:c>
-      <s:c r="B6" s="100"/>
-      <s:c r="C6" s="100"/>
-      <s:c r="D6" s="175"/>
-    </s:row>
-    <s:row r="7" ht="36.375" customHeight="1">
-      <s:c r="A7" s="96" t="s">
-        <s:v>3270</s:v>
-      </s:c>
-      <s:c r="B7" s="96">
-        <s:v>1</s:v>
-      </s:c>
       <s:c r="C7" s="174" t="s">
-        <s:v>3297</s:v>
+        <s:v>51</s:v>
       </s:c>
       <s:c r="D7" s="174"/>
     </s:row>
-    <s:row r="8" ht="36.375" customHeight="1">
+    <s:row r="8" ht="32.625" customHeight="1">
       <s:c r="A8" s="96" t="s">
-        <s:v>3250</s:v>
+        <s:v>3271</s:v>
       </s:c>
       <s:c r="B8" s="96">
-        <s:v>2</s:v>
+        <s:v>1</s:v>
       </s:c>
       <s:c r="C8" s="174" t="s">
-        <s:v>3327</s:v>
+        <s:v>3297</s:v>
       </s:c>
       <s:c r="D8" s="174"/>
     </s:row>
-    <s:row r="9" ht="36.375" customHeight="1">
+    <s:row r="9" ht="33.563" customHeight="1">
       <s:c r="A9" s="96" t="s">
         <s:v>3250</s:v>
       </s:c>
       <s:c r="B9" s="96">
-        <s:v>3</s:v>
+        <s:v>2</s:v>
       </s:c>
       <s:c r="C9" s="174" t="s">
-        <s:v>51</s:v>
+        <s:v>3475</s:v>
       </s:c>
       <s:c r="D9" s="174"/>
     </s:row>
-    <s:row r="10" ht="36.375" customHeight="1">
+    <s:row r="10" ht="32.625" customHeight="1">
       <s:c r="A10" s="96" t="s">
         <s:v>3252</s:v>
       </s:c>
@@ -12865,11 +13339,11 @@
         <s:v>1</s:v>
       </s:c>
       <s:c r="C10" s="174" t="s">
-        <s:v>3328</s:v>
+        <s:v>3475</s:v>
       </s:c>
       <s:c r="D10" s="174"/>
     </s:row>
-    <s:row r="11" ht="36.375" customHeight="1">
+    <s:row r="11" ht="33.563" customHeight="1">
       <s:c r="A11" s="96" t="s">
         <s:v>3252</s:v>
       </s:c>
@@ -12877,698 +13351,756 @@
         <s:v>3</s:v>
       </s:c>
       <s:c r="C11" s="174" t="s">
-        <s:v>3327</s:v>
+        <s:v>51</s:v>
       </s:c>
       <s:c r="D11" s="174"/>
     </s:row>
-    <s:row r="12" ht="36.375" customHeight="1">
+    <s:row r="12" ht="33.563" customHeight="1">
       <s:c r="A12" s="96" t="s">
-        <s:v>3330</s:v>
+        <s:v>3276</s:v>
       </s:c>
       <s:c r="B12" s="96">
         <s:v>3</s:v>
       </s:c>
       <s:c r="C12" s="174" t="s">
-        <s:v>2165</s:v>
+        <s:v>51</s:v>
       </s:c>
       <s:c r="D12" s="174"/>
     </s:row>
-    <s:row r="13" ht="36.375" customHeight="1">
+    <s:row r="13" ht="33.563" customHeight="1">
       <s:c r="A13" s="96" t="s">
-        <s:v>3276</s:v>
+        <s:v>3253</s:v>
       </s:c>
       <s:c r="B13" s="96">
-        <s:v>3</s:v>
+        <s:v>2</s:v>
       </s:c>
       <s:c r="C13" s="174" t="s">
-        <s:v>51</s:v>
+        <s:v>3476</s:v>
       </s:c>
       <s:c r="D13" s="174"/>
     </s:row>
-    <s:row r="14" ht="36.375" customHeight="1">
+    <s:row r="14" ht="33.563" customHeight="1">
       <s:c r="A14" s="96" t="s">
-        <s:v>38</s:v>
+        <s:v>3254</s:v>
       </s:c>
       <s:c r="B14" s="96">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C14" s="174" t="s">
-        <s:v>1500</s:v>
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C14" s="272" t="s">
+        <s:v>3421</s:v>
       </s:c>
       <s:c r="D14" s="174"/>
     </s:row>
-    <s:row r="15" ht="36.375" customHeight="1">
+    <s:row r="15" ht="33.563" customHeight="1">
       <s:c r="A15" s="96" t="s">
-        <s:v>38</s:v>
+        <s:v>3254</s:v>
       </s:c>
       <s:c r="B15" s="96">
         <s:v>3</s:v>
       </s:c>
       <s:c r="C15" s="174" t="s">
-        <s:v>3331</s:v>
+        <s:v>51</s:v>
       </s:c>
       <s:c r="D15" s="174"/>
     </s:row>
-    <s:row r="16" ht="36.375" customHeight="1">
+    <s:row r="16" ht="33.563" customHeight="1">
       <s:c r="A16" s="96" t="s">
-        <s:v>101</s:v>
+        <s:v>95</s:v>
       </s:c>
       <s:c r="B16" s="96">
-        <s:v>1</s:v>
+        <s:v>3</s:v>
       </s:c>
       <s:c r="C16" s="174" t="s">
-        <s:v>3332</s:v>
+        <s:v>3477</s:v>
       </s:c>
       <s:c r="D16" s="174"/>
     </s:row>
-    <s:row r="17" ht="36.375" customHeight="1">
+    <s:row r="17" ht="33.563" customHeight="1">
       <s:c r="A17" s="96" t="s">
-        <s:v>39</s:v>
+        <s:v>127</s:v>
       </s:c>
       <s:c r="B17" s="96">
         <s:v>2</s:v>
       </s:c>
       <s:c r="C17" s="174" t="s">
-        <s:v>3333</s:v>
+        <s:v>3313</s:v>
       </s:c>
       <s:c r="D17" s="174"/>
     </s:row>
-    <s:row r="18" ht="36.375" customHeight="1">
+    <s:row r="18" ht="33.563" customHeight="1">
       <s:c r="A18" s="96" t="s">
-        <s:v>109</s:v>
+        <s:v>110</s:v>
       </s:c>
       <s:c r="B18" s="96">
-        <s:v>2</s:v>
+        <s:v>1</s:v>
       </s:c>
       <s:c r="C18" s="174" t="s">
-        <s:v>3334</s:v>
+        <s:v>3478</s:v>
       </s:c>
       <s:c r="D18" s="174"/>
     </s:row>
-    <s:row r="19" ht="36.375" customHeight="1">
+    <s:row r="19" ht="33.563" customHeight="1">
       <s:c r="A19" s="96" t="s">
-        <s:v>218</s:v>
+        <s:v>158</s:v>
       </s:c>
       <s:c r="B19" s="96">
-        <s:v>2</s:v>
+        <s:v>1</s:v>
       </s:c>
       <s:c r="C19" s="174" t="s">
-        <s:v>3315</s:v>
+        <s:v>2890</s:v>
       </s:c>
       <s:c r="D19" s="174"/>
     </s:row>
-    <s:row r="20" ht="36.375" customHeight="1">
+    <s:row r="20" ht="33.563" customHeight="1">
       <s:c r="A20" s="96" t="s">
-        <s:v>112</s:v>
+        <s:v>158</s:v>
       </s:c>
       <s:c r="B20" s="96">
-        <s:v>1</s:v>
+        <s:v>3</s:v>
       </s:c>
       <s:c r="C20" s="174" t="s">
         <s:v>51</s:v>
       </s:c>
       <s:c r="D20" s="174"/>
     </s:row>
-    <s:row r="21" ht="36.375" customHeight="1">
+    <s:row r="21" ht="33.563" customHeight="1">
       <s:c r="A21" s="96" t="s">
-        <s:v>112</s:v>
+        <s:v>55</s:v>
       </s:c>
       <s:c r="B21" s="96">
-        <s:v>4</s:v>
+        <s:v>1</s:v>
       </s:c>
       <s:c r="C21" s="174" t="s">
-        <s:v>3335</s:v>
+        <s:v>1459</s:v>
       </s:c>
       <s:c r="D21" s="174"/>
     </s:row>
-    <s:row r="22" ht="36.375" customHeight="1">
+    <s:row r="22" ht="33.563" customHeight="1">
       <s:c r="A22" s="96" t="s">
-        <s:v>129</s:v>
+        <s:v>55</s:v>
       </s:c>
       <s:c r="B22" s="96">
-        <s:v>1</s:v>
+        <s:v>2</s:v>
       </s:c>
       <s:c r="C22" s="174" t="s">
-        <s:v>3336</s:v>
+        <s:v>3479</s:v>
       </s:c>
       <s:c r="D22" s="174"/>
     </s:row>
-    <s:row r="23" ht="36.375" customHeight="1">
+    <s:row r="23" ht="33.563" customHeight="1">
       <s:c r="A23" s="96" t="s">
-        <s:v>67</s:v>
+        <s:v>131</s:v>
       </s:c>
       <s:c r="B23" s="96">
-        <s:v>3</s:v>
+        <s:v>2</s:v>
       </s:c>
       <s:c r="C23" s="174" t="s">
-        <s:v>51</s:v>
+        <s:v>3481</s:v>
       </s:c>
       <s:c r="D23" s="174"/>
     </s:row>
-    <s:row r="24" ht="36.375" customHeight="1">
-      <s:c r="A24" s="96" t="s">
-        <s:v>21</s:v>
-      </s:c>
-      <s:c r="B24" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C24" s="174" t="s">
-        <s:v>3337</s:v>
-      </s:c>
-      <s:c r="D24" s="174"/>
+    <s:row r="24" ht="37.313" customHeight="1">
+      <s:c r="A24" s="99" t="s">
+        <s:v>391</s:v>
+      </s:c>
+      <s:c r="B24" s="100"/>
+      <s:c r="C24" s="100"/>
+      <s:c r="D24" s="99"/>
     </s:row>
-    <s:row r="25" ht="36.375" customHeight="1">
+    <s:row r="25" ht="27" customHeight="1">
       <s:c r="A25" s="96" t="s">
-        <s:v>75</s:v>
+        <s:v>3250</s:v>
       </s:c>
       <s:c r="B25" s="96">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="C25" s="174" t="s">
-        <s:v>3338</s:v>
-      </s:c>
-      <s:c r="D25" s="174"/>
+      <s:c r="C25" s="301" t="s">
+        <s:v>821</s:v>
+      </s:c>
+      <s:c r="D25" s="174" t="s">
+        <s:v>3282</s:v>
+      </s:c>
     </s:row>
-    <s:row r="26" ht="23.25" customHeight="1">
-      <s:c r="A26" s="99" t="s">
-        <s:v>391</s:v>
-      </s:c>
-      <s:c r="B26" s="100"/>
-      <s:c r="C26" s="100"/>
-      <s:c r="D26" s="99"/>
+    <s:row r="26" ht="27" customHeight="1">
+      <s:c r="A26" s="96" t="s">
+        <s:v>3250</s:v>
+      </s:c>
+      <s:c r="B26" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C26" s="301" t="s">
+        <s:v>1153</s:v>
+      </s:c>
+      <s:c r="D26" s="174" t="s">
+        <s:v>3285</s:v>
+      </s:c>
     </s:row>
     <s:row r="27" ht="27" customHeight="1">
-      <s:c r="A27" s="290" t="s">
-        <s:v>3295</s:v>
-      </s:c>
-      <s:c r="B27" s="291">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C27" s="292" t="s">
-        <s:v>226</s:v>
-      </s:c>
-      <s:c r="D27" s="45" t="s">
-        <s:v>3287</s:v>
+      <s:c r="A27" s="96" t="s">
+        <s:v>3251</s:v>
+      </s:c>
+      <s:c r="B27" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C27" s="301" t="s">
+        <s:v>820</s:v>
+      </s:c>
+      <s:c r="D27" s="174" t="s">
+        <s:v>3303</s:v>
       </s:c>
     </s:row>
     <s:row r="28" ht="27" customHeight="1">
-      <s:c r="A28" s="290" t="s">
-        <s:v>3271</s:v>
-      </s:c>
-      <s:c r="B28" s="291">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C28" s="292" t="s">
-        <s:v>901</s:v>
-      </s:c>
-      <s:c r="D28" s="45" t="s">
-        <s:v>3284</s:v>
+      <s:c r="A28" s="96" t="s">
+        <s:v>3251</s:v>
+      </s:c>
+      <s:c r="B28" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C28" s="301" t="s">
+        <s:v>821</s:v>
+      </s:c>
+      <s:c r="D28" s="174" t="s">
+        <s:v>3282</s:v>
       </s:c>
     </s:row>
     <s:row r="29" ht="27" customHeight="1">
-      <s:c r="A29" s="290" t="s">
-        <s:v>3249</s:v>
-      </s:c>
-      <s:c r="B29" s="291">
+      <s:c r="A29" s="96" t="s">
+        <s:v>3273</s:v>
+      </s:c>
+      <s:c r="B29" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C29" s="292" t="s">
-        <s:v>226</s:v>
-      </s:c>
-      <s:c r="D29" s="45" t="s">
-        <s:v>3287</s:v>
+      <s:c r="C29" s="301" t="s">
+        <s:v>168</s:v>
+      </s:c>
+      <s:c r="D29" s="174" t="s">
+        <s:v>3284</s:v>
       </s:c>
     </s:row>
     <s:row r="30" ht="27" customHeight="1">
-      <s:c r="A30" s="290" t="s">
-        <s:v>3250</s:v>
-      </s:c>
-      <s:c r="B30" s="291">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C30" s="292" t="s">
-        <s:v>1153</s:v>
-      </s:c>
-      <s:c r="D30" s="45" t="s">
-        <s:v>3285</s:v>
+      <s:c r="A30" s="96" t="s">
+        <s:v>3252</s:v>
+      </s:c>
+      <s:c r="B30" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C30" s="301" t="s">
+        <s:v>259</s:v>
+      </s:c>
+      <s:c r="D30" s="174" t="s">
+        <s:v>164</s:v>
       </s:c>
     </s:row>
     <s:row r="31" ht="27" customHeight="1">
-      <s:c r="A31" s="290" t="s">
-        <s:v>3251</s:v>
-      </s:c>
-      <s:c r="B31" s="291">
+      <s:c r="A31" s="96" t="s">
+        <s:v>3298</s:v>
+      </s:c>
+      <s:c r="B31" s="96">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C31" s="292" t="s">
+      <s:c r="C31" s="301" t="s">
         <s:v>1153</s:v>
       </s:c>
-      <s:c r="D31" s="45" t="s">
+      <s:c r="D31" s="174" t="s">
         <s:v>3285</s:v>
       </s:c>
     </s:row>
     <s:row r="32" ht="27" customHeight="1">
-      <s:c r="A32" s="290" t="s">
-        <s:v>3273</s:v>
-      </s:c>
-      <s:c r="B32" s="291">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C32" s="292" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D32" s="45" t="s">
-        <s:v>94</s:v>
+      <s:c r="A32" s="96" t="s">
+        <s:v>3277</s:v>
+      </s:c>
+      <s:c r="B32" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C32" s="301" t="s">
+        <s:v>1153</s:v>
+      </s:c>
+      <s:c r="D32" s="174" t="s">
+        <s:v>3285</s:v>
       </s:c>
     </s:row>
     <s:row r="33" ht="27" customHeight="1">
-      <s:c r="A33" s="290" t="s">
-        <s:v>3274</s:v>
-      </s:c>
-      <s:c r="B33" s="291">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C33" s="292" t="s">
-        <s:v>901</s:v>
-      </s:c>
-      <s:c r="D33" s="45" t="s">
-        <s:v>3284</s:v>
+      <s:c r="A33" s="96" t="s">
+        <s:v>3278</s:v>
+      </s:c>
+      <s:c r="B33" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C33" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D33" s="174" t="s">
+        <s:v>94</s:v>
       </s:c>
     </s:row>
     <s:row r="34" ht="27" customHeight="1">
-      <s:c r="A34" s="290" t="s">
-        <s:v>3274</s:v>
-      </s:c>
-      <s:c r="B34" s="291">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C34" s="292" t="s">
-        <s:v>1153</s:v>
-      </s:c>
-      <s:c r="D34" s="45" t="s">
-        <s:v>3285</s:v>
+      <s:c r="A34" s="96" t="s">
+        <s:v>95</s:v>
+      </s:c>
+      <s:c r="B34" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C34" s="301" t="s">
+        <s:v>288</s:v>
+      </s:c>
+      <s:c r="D34" s="174" t="s">
+        <s:v>3288</s:v>
       </s:c>
     </s:row>
     <s:row r="35" ht="27" customHeight="1">
-      <s:c r="A35" s="290" t="s">
-        <s:v>3252</s:v>
-      </s:c>
-      <s:c r="B35" s="291">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C35" s="292" t="s">
-        <s:v>1035</s:v>
-      </s:c>
-      <s:c r="D35" s="45" t="s">
-        <s:v>3280</s:v>
+      <s:c r="A35" s="96" t="s">
+        <s:v>127</s:v>
+      </s:c>
+      <s:c r="B35" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C35" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D35" s="174" t="s">
+        <s:v>3286</s:v>
       </s:c>
     </s:row>
     <s:row r="36" ht="27" customHeight="1">
-      <s:c r="A36" s="290" t="s">
-        <s:v>3298</s:v>
-      </s:c>
-      <s:c r="B36" s="291">
+      <s:c r="A36" s="96" t="s">
+        <s:v>101</s:v>
+      </s:c>
+      <s:c r="B36" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C36" s="292" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D36" s="45" t="s">
-        <s:v>123</s:v>
+      <s:c r="C36" s="301" t="s">
+        <s:v>497</s:v>
+      </s:c>
+      <s:c r="D36" s="174" t="s">
+        <s:v>3289</s:v>
       </s:c>
     </s:row>
     <s:row r="37" ht="27" customHeight="1">
-      <s:c r="A37" s="290" t="s">
-        <s:v>3254</s:v>
-      </s:c>
-      <s:c r="B37" s="291">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C37" s="292" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D37" s="45" t="s">
-        <s:v>94</s:v>
+      <s:c r="A37" s="96" t="s">
+        <s:v>104</s:v>
+      </s:c>
+      <s:c r="B37" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C37" s="301" t="s">
+        <s:v>497</s:v>
+      </s:c>
+      <s:c r="D37" s="174" t="s">
+        <s:v>3289</s:v>
       </s:c>
     </s:row>
     <s:row r="38" ht="27" customHeight="1">
-      <s:c r="A38" s="290" t="s">
-        <s:v>95</s:v>
-      </s:c>
-      <s:c r="B38" s="291">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C38" s="292" t="s">
-        <s:v>1035</s:v>
-      </s:c>
-      <s:c r="D38" s="45" t="s">
-        <s:v>3280</s:v>
+      <s:c r="A38" s="96" t="s">
+        <s:v>104</s:v>
+      </s:c>
+      <s:c r="B38" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C38" s="301" t="s">
+        <s:v>497</s:v>
+      </s:c>
+      <s:c r="D38" s="174" t="s">
+        <s:v>3289</s:v>
       </s:c>
     </s:row>
     <s:row r="39" ht="27" customHeight="1">
-      <s:c r="A39" s="290" t="s">
-        <s:v>95</s:v>
-      </s:c>
-      <s:c r="B39" s="291">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C39" s="292" t="s">
+      <s:c r="A39" s="96" t="s">
+        <s:v>104</s:v>
+      </s:c>
+      <s:c r="B39" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C39" s="301" t="s">
         <s:v>2583</s:v>
       </s:c>
-      <s:c r="D39" s="45" t="s">
-        <s:v>123</s:v>
+      <s:c r="D39" s="174" t="s">
+        <s:v>164</s:v>
       </s:c>
     </s:row>
     <s:row r="40" ht="27" customHeight="1">
-      <s:c r="A40" s="290" t="s">
-        <s:v>104</s:v>
-      </s:c>
-      <s:c r="B40" s="291">
+      <s:c r="A40" s="96" t="s">
+        <s:v>39</s:v>
+      </s:c>
+      <s:c r="B40" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C40" s="292" t="s">
-        <s:v>1139</s:v>
-      </s:c>
-      <s:c r="D40" s="45" t="s">
-        <s:v>3289</s:v>
+      <s:c r="C40" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D40" s="174" t="s">
+        <s:v>123</s:v>
       </s:c>
     </s:row>
     <s:row r="41" ht="27" customHeight="1">
-      <s:c r="A41" s="290" t="s">
+      <s:c r="A41" s="96" t="s">
         <s:v>109</s:v>
       </s:c>
-      <s:c r="B41" s="291">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C41" s="292" t="s">
-        <s:v>752</s:v>
-      </s:c>
-      <s:c r="D41" s="45" t="s">
+      <s:c r="B41" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C41" s="301" t="s">
+        <s:v>173</s:v>
+      </s:c>
+      <s:c r="D41" s="174" t="s">
         <s:v>663</s:v>
       </s:c>
     </s:row>
     <s:row r="42" ht="27" customHeight="1">
-      <s:c r="A42" s="290" t="s">
-        <s:v>110</s:v>
-      </s:c>
-      <s:c r="B42" s="291">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C42" s="292" t="s">
-        <s:v>113</s:v>
-      </s:c>
-      <s:c r="D42" s="45" t="s">
-        <s:v>114</s:v>
+      <s:c r="A42" s="96" t="s">
+        <s:v>111</s:v>
+      </s:c>
+      <s:c r="B42" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C42" s="301" t="s">
+        <s:v>352</s:v>
+      </s:c>
+      <s:c r="D42" s="174" t="s">
+        <s:v>121</s:v>
       </s:c>
     </s:row>
     <s:row r="43" ht="27" customHeight="1">
-      <s:c r="A43" s="290" t="s">
-        <s:v>111</s:v>
-      </s:c>
-      <s:c r="B43" s="291">
-        <s:v>2.3</s:v>
-      </s:c>
-      <s:c r="C43" s="292" t="s">
-        <s:v>352</s:v>
-      </s:c>
-      <s:c r="D43" s="45" t="s">
-        <s:v>121</s:v>
+      <s:c r="A43" s="96" t="s">
+        <s:v>43</s:v>
+      </s:c>
+      <s:c r="B43" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C43" s="301" t="s">
+        <s:v>168</s:v>
+      </s:c>
+      <s:c r="D43" s="174" t="s">
+        <s:v>824</s:v>
       </s:c>
     </s:row>
     <s:row r="44" ht="27" customHeight="1">
-      <s:c r="A44" s="290" t="s">
-        <s:v>41</s:v>
-      </s:c>
-      <s:c r="B44" s="291">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C44" s="292" t="s">
-        <s:v>113</s:v>
-      </s:c>
-      <s:c r="D44" s="45" t="s">
-        <s:v>114</s:v>
+      <s:c r="A44" s="96" t="s">
+        <s:v>43</s:v>
+      </s:c>
+      <s:c r="B44" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C44" s="301" t="s">
+        <s:v>229</s:v>
+      </s:c>
+      <s:c r="D44" s="174" t="s">
+        <s:v>3290</s:v>
       </s:c>
     </s:row>
     <s:row r="45" ht="27" customHeight="1">
-      <s:c r="A45" s="290" t="s">
-        <s:v>43</s:v>
-      </s:c>
-      <s:c r="B45" s="291">
-        <s:v>2.3</s:v>
-      </s:c>
-      <s:c r="C45" s="292" t="s">
-        <s:v>386</s:v>
-      </s:c>
-      <s:c r="D45" s="45" t="s">
-        <s:v>3290</s:v>
+      <s:c r="A45" s="96" t="s">
+        <s:v>46</s:v>
+      </s:c>
+      <s:c r="B45" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C45" s="301" t="s">
+        <s:v>113</s:v>
+      </s:c>
+      <s:c r="D45" s="174" t="s">
+        <s:v>114</s:v>
       </s:c>
     </s:row>
     <s:row r="46" ht="27" customHeight="1">
-      <s:c r="A46" s="290" t="s">
+      <s:c r="A46" s="96" t="s">
         <s:v>48</s:v>
       </s:c>
-      <s:c r="B46" s="291">
+      <s:c r="B46" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C46" s="292" t="s">
-        <s:v>1035</s:v>
-      </s:c>
-      <s:c r="D46" s="45" t="s">
-        <s:v>3280</s:v>
+      <s:c r="C46" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D46" s="302" t="s">
+        <s:v>96</s:v>
       </s:c>
     </s:row>
     <s:row r="47" ht="27" customHeight="1">
-      <s:c r="A47" s="290" t="s">
-        <s:v>3340</s:v>
-      </s:c>
-      <s:c r="B47" s="291">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C47" s="292" t="s">
-        <s:v>229</s:v>
-      </s:c>
-      <s:c r="D47" s="45" t="s">
-        <s:v>224</s:v>
+      <s:c r="A47" s="96" t="s">
+        <s:v>128</s:v>
+      </s:c>
+      <s:c r="B47" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C47" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D47" s="174" t="s">
+        <s:v>94</s:v>
       </s:c>
     </s:row>
     <s:row r="48" ht="27" customHeight="1">
-      <s:c r="A48" s="290" t="s">
-        <s:v>218</s:v>
-      </s:c>
-      <s:c r="B48" s="291">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C48" s="292" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D48" s="45" t="s">
-        <s:v>123</s:v>
+      <s:c r="A48" s="96" t="s">
+        <s:v>112</s:v>
+      </s:c>
+      <s:c r="B48" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C48" s="301" t="s">
+        <s:v>462</s:v>
+      </s:c>
+      <s:c r="D48" s="174" t="s">
+        <s:v>17</s:v>
       </s:c>
     </s:row>
     <s:row r="49" ht="27" customHeight="1">
-      <s:c r="A49" s="290" t="s">
+      <s:c r="A49" s="96" t="s">
         <s:v>112</s:v>
       </s:c>
-      <s:c r="B49" s="291">
+      <s:c r="B49" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C49" s="292" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D49" s="45" t="s">
-        <s:v>3286</s:v>
+      <s:c r="C49" s="301" t="s">
+        <s:v>462</s:v>
+      </s:c>
+      <s:c r="D49" s="174" t="s">
+        <s:v>17</s:v>
       </s:c>
     </s:row>
     <s:row r="50" ht="27" customHeight="1">
-      <s:c r="A50" s="290" t="s">
-        <s:v>52</s:v>
-      </s:c>
-      <s:c r="B50" s="291">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C50" s="292" t="s">
-        <s:v>352</s:v>
-      </s:c>
-      <s:c r="D50" s="45" t="s">
-        <s:v>121</s:v>
+      <s:c r="A50" s="96" t="s">
+        <s:v>50</s:v>
+      </s:c>
+      <s:c r="B50" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C50" s="301" t="s">
+        <s:v>228</s:v>
+      </s:c>
+      <s:c r="D50" s="174" t="s">
+        <s:v>181</s:v>
       </s:c>
     </s:row>
     <s:row r="51" ht="27" customHeight="1">
-      <s:c r="A51" s="290" t="s">
-        <s:v>55</s:v>
-      </s:c>
-      <s:c r="B51" s="291">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C51" s="292" t="s">
-        <s:v>1139</s:v>
-      </s:c>
-      <s:c r="D51" s="45" t="s">
-        <s:v>3289</s:v>
+      <s:c r="A51" s="96" t="s">
+        <s:v>52</s:v>
+      </s:c>
+      <s:c r="B51" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C51" s="301" t="s">
+        <s:v>352</s:v>
+      </s:c>
+      <s:c r="D51" s="174" t="s">
+        <s:v>121</s:v>
       </s:c>
     </s:row>
     <s:row r="52" ht="27" customHeight="1">
-      <s:c r="A52" s="290" t="s">
+      <s:c r="A52" s="96" t="s">
         <s:v>55</s:v>
       </s:c>
-      <s:c r="B52" s="291">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C52" s="292" t="s">
-        <s:v>905</s:v>
-      </s:c>
-      <s:c r="D52" s="45" t="s">
-        <s:v>3289</s:v>
+      <s:c r="B52" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C52" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D52" s="174" t="s">
+        <s:v>3286</s:v>
       </s:c>
     </s:row>
     <s:row r="53" ht="27" customHeight="1">
-      <s:c r="A53" s="290" t="s">
-        <s:v>60</s:v>
-      </s:c>
-      <s:c r="B53" s="291">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C53" s="292" t="s">
-        <s:v>229</s:v>
-      </s:c>
-      <s:c r="D53" s="45" t="s">
-        <s:v>224</s:v>
+      <s:c r="A53" s="96" t="s">
+        <s:v>115</s:v>
+      </s:c>
+      <s:c r="B53" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C53" s="301" t="s">
+        <s:v>113</s:v>
+      </s:c>
+      <s:c r="D53" s="174" t="s">
+        <s:v>114</s:v>
       </s:c>
     </s:row>
     <s:row r="54" ht="27" customHeight="1">
-      <s:c r="A54" s="290" t="s">
-        <s:v>62</s:v>
-      </s:c>
-      <s:c r="B54" s="291">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C54" s="292" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D54" s="45" t="s">
-        <s:v>3286</s:v>
+      <s:c r="A54" s="96" t="s">
+        <s:v>115</s:v>
+      </s:c>
+      <s:c r="B54" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C54" s="301" t="s">
+        <s:v>113</s:v>
+      </s:c>
+      <s:c r="D54" s="174" t="s">
+        <s:v>114</s:v>
       </s:c>
     </s:row>
     <s:row r="55" ht="27" customHeight="1">
-      <s:c r="A55" s="290" t="s">
-        <s:v>187</s:v>
-      </s:c>
-      <s:c r="B55" s="291">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C55" s="292" t="s">
-        <s:v>386</s:v>
-      </s:c>
-      <s:c r="D55" s="45" t="s">
-        <s:v>3290</s:v>
+      <s:c r="A55" s="96" t="s">
+        <s:v>237</s:v>
+      </s:c>
+      <s:c r="B55" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C55" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D55" s="302" t="s">
+        <s:v>96</s:v>
       </s:c>
     </s:row>
     <s:row r="56" ht="27" customHeight="1">
-      <s:c r="A56" s="290" t="s">
-        <s:v>78</s:v>
-      </s:c>
-      <s:c r="B56" s="291">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C56" s="292" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D56" s="45" t="s">
-        <s:v>94</s:v>
+      <s:c r="A56" s="96" t="s">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="B56" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C56" s="301" t="s">
+        <s:v>3292</s:v>
+      </s:c>
+      <s:c r="D56" s="174" t="s">
+        <s:v>224</s:v>
       </s:c>
     </s:row>
     <s:row r="57" ht="27" customHeight="1">
-      <s:c r="A57" s="290" t="s">
-        <s:v>78</s:v>
-      </s:c>
-      <s:c r="B57" s="291">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C57" s="292" t="s">
-        <s:v>117</s:v>
-      </s:c>
-      <s:c r="D57" s="45" t="s">
-        <s:v>825</s:v>
+      <s:c r="A57" s="241" t="s">
+        <s:v>62</s:v>
+      </s:c>
+      <s:c r="B57" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C57" s="301" t="s">
+        <s:v>229</s:v>
+      </s:c>
+      <s:c r="D57" s="174" t="s">
+        <s:v>3290</s:v>
       </s:c>
     </s:row>
     <s:row r="58" ht="27" customHeight="1">
-      <s:c r="A58" s="290" t="s">
-        <s:v>78</s:v>
-      </s:c>
-      <s:c r="B58" s="291">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C58" s="292" t="s">
-        <s:v>229</s:v>
-      </s:c>
-      <s:c r="D58" s="45" t="s">
-        <s:v>224</s:v>
+      <s:c r="A58" s="241" t="s">
+        <s:v>187</s:v>
+      </s:c>
+      <s:c r="B58" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C58" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D58" s="302" t="s">
+        <s:v>96</s:v>
       </s:c>
     </s:row>
     <s:row r="59" ht="27" customHeight="1">
-      <s:c r="A59" s="290" t="s">
-        <s:v>131</s:v>
-      </s:c>
-      <s:c r="B59" s="291">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C59" s="292" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D59" s="45" t="s">
-        <s:v>3286</s:v>
+      <s:c r="A59" s="241" t="s">
+        <s:v>187</s:v>
+      </s:c>
+      <s:c r="B59" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C59" s="301" t="s">
+        <s:v>229</s:v>
+      </s:c>
+      <s:c r="D59" s="174" t="s">
+        <s:v>3290</s:v>
       </s:c>
     </s:row>
     <s:row r="60" ht="27" customHeight="1">
-      <s:c r="A60" s="290" t="s">
-        <s:v>18</s:v>
-      </s:c>
-      <s:c r="B60" s="291">
+      <s:c r="A60" s="241" t="s">
+        <s:v>71</s:v>
+      </s:c>
+      <s:c r="B60" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C60" s="292" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D60" s="45" t="s">
-        <s:v>96</s:v>
+      <s:c r="C60" s="301" t="s">
+        <s:v>1322</s:v>
+      </s:c>
+      <s:c r="D60" s="174" t="s">
+        <s:v>3291</s:v>
       </s:c>
     </s:row>
     <s:row r="61" ht="27" customHeight="1">
-      <s:c r="B61"/>
-      <s:c r="D61" s="35"/>
+      <s:c r="A61" s="241" t="s">
+        <s:v>73</s:v>
+      </s:c>
+      <s:c r="B61" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C61" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D61" s="174" t="s">
+        <s:v>3286</s:v>
+      </s:c>
     </s:row>
     <s:row r="62" ht="27" customHeight="1">
-      <s:c r="D62" s="35"/>
+      <s:c r="A62" s="241" t="s">
+        <s:v>75</s:v>
+      </s:c>
+      <s:c r="B62" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C62" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D62" s="174" t="s">
+        <s:v>123</s:v>
+      </s:c>
     </s:row>
     <s:row r="63" ht="27" customHeight="1">
-      <s:c r="D63" s="35"/>
+      <s:c r="A63" s="241" t="s">
+        <s:v>75</s:v>
+      </s:c>
+      <s:c r="B63" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C63" s="301" t="s">
+        <s:v>352</s:v>
+      </s:c>
+      <s:c r="D63" s="174" t="s">
+        <s:v>121</s:v>
+      </s:c>
     </s:row>
-    <s:row r="64" ht="21.75" customHeight="1">
-      <s:c r="D64" s="35"/>
+    <s:row r="64" ht="27" customHeight="1">
+      <s:c r="A64" s="241" t="s">
+        <s:v>80</s:v>
+      </s:c>
+      <s:c r="B64" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C64" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D64" s="174" t="s">
+        <s:v>123</s:v>
+      </s:c>
     </s:row>
-    <s:row r="65" ht="21" customHeight="1">
-      <s:c r="D65" s="35"/>
+    <s:row r="65" ht="27" customHeight="1">
+      <s:c r="A65" s="241" t="s">
+        <s:v>220</s:v>
+      </s:c>
+      <s:c r="B65" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C65" s="301" t="s">
+        <s:v>2583</s:v>
+      </s:c>
+      <s:c r="D65" s="174" t="s">
+        <s:v>94</s:v>
+      </s:c>
     </s:row>
-    <s:row r="67" ht="13.5"/>
-    <s:row r="68" ht="13.5"/>
-    <s:row r="69" ht="13.5"/>
-    <s:row r="70" ht="13.5"/>
-    <s:row r="71" ht="13.5"/>
-    <s:row r="72" ht="13.5"/>
-    <s:row r="73" ht="13.5"/>
-    <s:row r="74" ht="13.5"/>
-    <s:row r="75" ht="13.5"/>
-    <s:row r="76" ht="13.5"/>
+    <s:row r="66" ht="27" customHeight="1">
+      <s:c r="A66" s="241" t="s">
+        <s:v>220</s:v>
+      </s:c>
+      <s:c r="B66" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C66" s="301" t="s">
+        <s:v>821</s:v>
+      </s:c>
+      <s:c r="D66" s="174" t="s">
+        <s:v>3282</s:v>
+      </s:c>
+    </s:row>
   </s:sheetData>
-  <s:autoFilter ref="A1:D65">
-    <s:filterColumn colId="2" showButton="0"/>
-  </s:autoFilter>
-  <s:mergeCells count="5">
+  <s:mergeCells count="4">
     <s:mergeCell ref="C1:D1"/>
-    <s:mergeCell ref="A2:D2"/>
-    <s:mergeCell ref="A4:D4"/>
-    <s:mergeCell ref="A6:D6"/>
-    <s:mergeCell ref="A26:D26"/>
+    <s:mergeCell ref="A3:D3"/>
+    <s:mergeCell ref="A5:D5"/>
+    <s:mergeCell ref="A24:D24"/>
   </s:mergeCells>
   <s:printOptions headings="0" gridLines="0"/>
   <s:pageMargins left="0.701" right="0.701" top="0.752" bottom="0.752" header="0.3" footer="0.3"/>

--- a/runtime/downloaded/Новая таблица (25).xlsx
+++ b/runtime/downloaded/Новая таблица (25).xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<s:workbook xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <s:workbookPr/>
   <s:bookViews>
     <s:workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
@@ -9,7 +9,7 @@
     <s:sheet name="замена" sheetId="1" state="visible" r:id="rId1"/>
   </s:sheets>
   <s:definedNames>
-    <s:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">замена!$A$1:$D$75</s:definedName>
+    <s:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">замена!$A$1:$D$77</s:definedName>
     <s:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">замена!$A$1:$D$76</s:definedName>
     <s:definedName name="Диапазон_2">#REF!</s:definedName>
   </s:definedNames>
@@ -10906,11 +10906,613 @@
   <s:si>
     <s:t>Уарамзина К.Н.</s:t>
   </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 29.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.05 География Куркова А.И. УЛК2,ауд. 208</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 11 Физика Князева П.Г. 1ОБЩ-АУД.35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 10 Основы безопасности и защита Родины Епифанцева Е.В. УЛК2,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.04 Основы алгоритмизации и программирования Шишанова Т.В. УЛК1,ауд.408</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.02 Инженерно-геодезические работы при проектировании зданий и инженерных сооружений
+Чернова К.А. УПМ-207</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01 Эксплуатация и обслуживание линий электропередач  Киргинцев Д.Е. УПМ-211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 30.09 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОМД-561</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ПГ=-Д</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Елхова Г.А. УЛК2,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 История Боженко И.И. УЛК2,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 09 Физическая культура Стадник А.П. с/з2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Галицкова А.В. УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 06.01 Монтажник каркасно-обшивных конструкций Васянкина В.С. УПМ,ауд.111</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.04 Физическая культура Масленников А.Е. с/з1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Правовое регулирование отношений в землеустройстве, кадастре и градостроительстве Ноздреватых У.А. УЛК1,ауд.020</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01 Содержание, контроль и техническая эксплуатация жилищного фонда Цыганков М.Е.УЛК1,ауд.013</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.08 Основы финансовой грамотности Пухляр И.Н. УЛК1,ауд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.08 Основы финансовой грамотности Пухляр И.Н. УЛК1,ауд.016</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 06.01 Монтажник каркасно-обшивных конструкций Бурылев Т.Д. УЛК1,ауд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 06.01 Монтажник каркасно-обшивных конструкций Бурылев Т.Д. УПМ-207</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Нормативное обеспечение процесса технической эксплуатации гражданских зданий  Зинкевич Н.С. УЛК1,ауд.020</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.05 Основы автоматики и элементы систем автоматического регулирования Киргинцев Д.Е. УПМ-211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Проектирование и создание геодезических опорных, специального назначения, нивелирных, гравиметрических сетейКириллов А.Б. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Проектирование и создание геодезических опорных, специального назначения, нивелирных, гравиметрических сетей Кириллов А.Б. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">СГ.04 Физическая культура Масленников А.Е. </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 09 Физическая культура Стадник А.П. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.04 Физическая культура Масленников А.Е. с/з2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 09 Физическая культура Стадник А.П. с/з1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 01.10 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СЭЗ-ДЖ51</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 09 Физическая культура Стадник А.П. т/з</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.01 Русский  язык  Елхова Г.А. УПМ-105  </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.01 Технология выполнения поисково-разведочных работ Ащаулова Я.Н.УЛК1,ауд.409</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.01 Инженерная графика Донских Е.С. УЛК1,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 06.01 Монтажник каркасно-обшивных конструкций Силина Е.М. УЛК1,ауд.410</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Разработка объемно-планировочных и конструктивных решений различных объектов капитального строительства Бурылев Т.Д. УПМ-207</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Математическая обработка результатов геодезических  измерений  
+Матвеева И.И. УЛК1,ауд.411</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.04 Электронные геодезические средства измерений Бикбаева Д.Д. УЛК1,ауд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.04 Электронные геодезические средства измерений Бикбаева Д.Д. УПМ-204</s:t>
+  </s:si>
+  <s:si>
+    <s:r>
+      <s:rPr>
+        <s:rFont val="Tinos"/>
+        <s:b val="1"/>
+        <s:color rgb="FF000000"/>
+        <s:sz val="14"/>
+        <s:vertAlign val="baseline"/>
+        <s:scheme val="minor"/>
+      </s:rPr>
+      <s:t>СЭЗ-Д621</s:t>
+    </s:r>
+  </s:si>
+  <s:si>
+    <s:r>
+      <s:rPr>
+        <s:rFont val="Tinos"/>
+        <s:b val="1"/>
+        <s:color rgb="FF000000"/>
+        <s:sz val="14"/>
+        <s:vertAlign val="baseline"/>
+        <s:scheme val="minor"/>
+      </s:rPr>
+      <s:t>СЭЗ-Д62</s:t>
+    </s:r>
+  </s:si>
+  <s:si>
+    <s:t>Карамзина К.С.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с/з</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 02.10 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика Орлова Е.Р..УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.05 География Куркова А.И. Упм-105</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 09 Физическая культура Стадник А.П. С/з2</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01Русский  язык  Семенова О.В. УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.01 Аналитическая химия Коробкова М.Н. УЛК2,ауд.208</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.03 Основы гегодезии и картографии Ляхов А.К. УЛК2,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.02 Общая технология электромонтажных работ Сапожников В.В. УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.02 Монтаж, наладка и эксплуатация электрооборудования Сапожников В.В. УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.01 Инженерные изыскания в строительстве Матвеева И.И. УЛК1,ауд.411</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.03 Психология общения                               Куркова А.Н.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОГСЭ.03 Психология общения     Куркова А.Н. УПМ-105</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.11 Основы предпринимательской деятельности Коленкович М.Д.УЛК1,ауд.110</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 08 Информатика Шевчук О.П.УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.08 Основы финансовой грамотности Пухляр И.Н. УЛК1,ауд.013</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 03.10 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 05.10 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.04 Этика профессиональной деятельности Цыганков М.Е.. УЛК1,ауд.013</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 03.01 Организация работ связанных с соблюдением санитарного содержания общего имущества Цыганков М.Е.УЛК1,ауд.013 </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">СГ.05 Основы финансовой грамотности Пухляр И.Н. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.02 Основы электротехники  Киргинцев Д.Е.  УПМ-211</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОП.02 Основы электротехники    Киргинцев Д.Е.  </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОП.02 Основы электротехники  Киргинцев Д.Е.  </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Организация работ связанных с соблюдением санитарного содержания общего имущества Цыганков М.Е.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 01.01 Обеспечение ведения управления многоквартирным домом и  домашним хозяйством Кузнецов А.В. </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОП.04 Этика профессиональной деятельности Цыганков М.Е.. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Разработка объемно-планировочных и конструктивных решений различных объектов капитального строительства Чубцов К.В</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД. 12 Химия Коробкова М.Н. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Проектирование и создание геодезических опорных, специального назначения, нивелирных, гравиметрических сетей
+Кириллов А.Б. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОП.13 Основы предпринимательской деятельности Коленкович М.Д.УЛК1,ауд.110 </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.13 Основы предпринимательской деятельности Коленкович М.Д.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.11 Основы предпринимательской деятельности Коленкович М.Д.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 01.01 Проектирование и создание геодезических опорных, специального назначения, нивелирных, гравиметрических сетей Кириллов А.Б. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 04  Обществознание Левочкина П.Е. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.04 Геология Гурулева Е.А. УЛК1,ауд.104</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.01 Матеамтические методы решения прикладных профессиональных задач Трофимчук Д.П. УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.02 Иностранный язык в профессиональной деятельности Отт А.А. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Топографо-геодезические изыскания Аникина И.В. УЛК1,ауд.414</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.02 Управление автоматизированными системами вентиляции и кондиционирования воздуха Зинкевич Н.С. УЛК1,ауд.020</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1общ.ауд.35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>К</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 История  Левочкина П.Е. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 история  Левочкина П.Е. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01 Технология топографических съемок УЛК1,ауд.407</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.07 Правовое обеспечение проф. деятельности Кузнецов А.В. УЛК1,ауд.408</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.03 Иванов Н.А. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 06.10 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>3-5пары</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-19.10 УЛК1,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-19.10 УЛК1,ауд.309 (3-5 пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СЗ-Д41</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МСУ-Д6</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1общ-12ауд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Гу</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Иванов Н.А</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 03 История Левочкина П.Е. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.04 Обществознание </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.04 Обществознание Левочкина П.Е. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">СГ.05 Основы финансовой грамотности Ловыгина И.А. УЛК1,ауд.310    </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.01 Матеамтические методы решения прикладных профессиональных задач Трофимчук Д.П. УПМ-209</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.01 Замерщик  на топографо-геодезических  и  маркшейдерских работах Бикбаева Д.Д. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.02 Иностранный язык в профессиональной деятельности
+Отт А.А. УЛК2,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.03 Инженерно-геодезические работы при строительстве зданий и инженерных сооружений Матвеева И.И..УЛК1,ауд.411</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УП.09</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">с 6.10-12.10 </s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-12.10 УЛК1,ауд.406 (4-6 пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.01 Замерщик  на топографо-геодезических  и  маркшейдерских работах Бикбаева Д.Д. УПМ-204</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 07.10 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-12.10 УЛК1,ауд.406 ( пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-19.10 УЛК1,ауд.309 ( пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-19.10 УЛК1,ауд.309 (4-6 пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.02 Основы геодезии, картографии и маркшейдерского дела Иванов Н.А. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Правовое регулирование отношений в землеустройстве, кадастре и градостроительстве Первых Т.П.УЛК1,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Проектирование и создание геодезических опорных, специального назначения, нивелирных, гравиметрических сетей Иванов Н.А. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.02 Инженерно-геодезические работы при проектировании зданий и инженерных сооружений
+Чернова К.А. УЛК1,ауд.020</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОМД-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>1общ-ауд.35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.05 Основы геологии, геоморфологии, почвоведения Гурулева Е.А. УЛК1,ауд.309</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.04 Здания и сооружения Матвеева И.И. УЛК1,ауд.312</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 08.10 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-19.10 УЛК1,ауд.309 (</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-12.10 УЛК1,ауд.406 (</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-12.10 УЛК1,ауд.406 (3-5пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-19.10 УЛК1,ауд.309 (2-4 пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ГС-Д61МД-Д61</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.11 Физика Елхов Н.А..УЛК2,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.01  Горнорабочий на геологических работахАникина И.В. УЛК1,ауд.414</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 05.01  Горнорабочий на геологических работах Аникина И.В. УЛК1,ауд.414</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve"> СГ.04 Физическая культура Севостьянова Ю.Б. с/з1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.01 История России Чаплыгина Н.А. УЛК2,ауд.308</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.03 Основы гегодезии и картографии Ляхов А.К. УЛК2,ауд.306</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Математическая обработка результатов геодезических  измерений   Матвеева И.И. УЛК1,ауд.411</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 08.01 Проектирование и разработка интерфейсов пользователя Насонова Н.А. УЛК1,ауд.402  </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.02 Инженерно-геодезические работы при проектировании зданий и инженерных сооружений
+Чернова К.А. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.08 Шевчук О.П. .УЛК2,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 09.10 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-12.10 УЛК1,ауд.406 (пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-12.10 УЛК1,ауд.406 (4-6пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-19.10 УЛК1,ауд.309 ( 2-4 пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД. 04 Обществознание Левочкина П.Е. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.04 Физическая культура
+Карамзина К.Н. с/з1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.04 Физическая культура Карамзина К.Н. с/з1</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Топографо-геодезические изыскания Аникина И.В. УЛК1,ауд.409</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.07 Правовое обеспечение профессиональной деятельности     Кузнецов А.В. УЛК1,ауд.305</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.02 Иностранный язык в профессиональной деятельности Чабунина О.А. общ2-25</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.01 Организация геодезического производства и охрана труда Иванов Н.А. УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК1,ауд.111</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УПМ,ауд.111</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 10.10 (ЗНАМЕНАТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-19.10 УЛК1,ауд.309 ( 4-6 пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01Русский  язык Семенова О.В. УЛК2,ауд.203</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.01 Русский  язык  Стафеева Е.М. улк2,ауд.202а</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.06 Иностранный язык Толызенкова А.А. УЛК2,ауд.211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.01 История России Левочкина П.Е. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Лабораторные методы геологических исследований Лешкевич О.П. УПМ-105</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.02 Инженерно-геодезические работы при проектировании зданий и инженерных сооружений
+Иванов Н.А. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 04.03 Инженерно-геодезические работы при строительстве зданий и инженерных сооружений </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 04.03 Инженерно-геодезические работы при строительстве зданий и инженерных сооружений Иванов Н.А. УЛК1,ауд.405</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МСП-Д41</s:t>
+  </s:si>
+  <s:si>
+    <s:r>
+      <s:rPr>
+        <s:rFont val="Tinos"/>
+        <s:color rgb="FF000000"/>
+        <s:sz val="14"/>
+        <s:vertAlign val="baseline"/>
+        <s:scheme val="minor"/>
+      </s:rPr>
+      <s:t xml:space="preserve">УЛК2,ауд.202а </s:t>
+    </s:r>
+  </s:si>
+  <s:si>
+    <s:t>Орлова Е.М.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ЗАМЕНА НА 12.10 (ЧИСЛИТЕЛЬ)</s:t>
+  </s:si>
+  <s:si>
+    <s:t>с 6.10-12.10 УЛК1,ауд.406 (2-4 пары)</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.03 История </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.03 История Левочкина П.Е. УЛК2,ауд.310</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОД.01 Русский  язык  Елхова Г.А. 1общ-ауд.12 </s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.03 Основы электротехники и электроника Киргинцев Д.Е. УПМ-211</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.01 Разработка объемно-планировочных и конструктивных решений различных объектов капитального строительства Силина Е.М. УЛК1,ауд.410</s:t>
+  </s:si>
+  <s:si>
+    <s:t>СГ.06 Основы финансовой грамотности Онищнко Н.Н. УЛК1,ауд.112</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">МДК 08.02 Графический дизайн и мультимедиа Савченко А.И. УЛК1,ауд.407    </s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 08.01 Проектирование и разработка интерфейсов пользователяШишанова Т.В. УЛК1,ауд.408</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02 02 Графическое и цифровое оформление результатов топографических съемок Теличкина И.П. УЛК1,ауд.020</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 09.03 Обеспечение безопасности веб-приложений.
+Насонова Н.А. УЛК1,ауд.402</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 09.03 Обеспечение безопасности веб-приложений. Насонова Н.А. УЛК1,ауд.402</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 03.02 Монтаж, наладка и эксплуатация электрических сетей Сапожников В.В. УПМ-210</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 01.02 Проектирование инженерных сооружений     Чубцов К.В. УЛК1,ауд.307</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК2,ауд.0</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК1,ауд.112</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Попови чА.Н.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>УЛК1,ауд.103</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОП.08 Информатика Шевчук О.П. УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОД.08 Информатика Шевчук О.П. УЛК2,ауд.302</s:t>
+  </s:si>
+  <s:si>
+    <s:t>МДК 02.01 Маркшейдерское  обеспечение  ведения  горных работ Аникина И.В. УЛК1,ауд.402</s:t>
+  </s:si>
 </s:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<s:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<s:styleSheet xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <s:numFmts count="5">
     <s:numFmt numFmtId="160" formatCode="dd/mmm"/>
     <s:numFmt numFmtId="161" formatCode="[$-F400]h:mm:ss"/>
@@ -10918,7 +11520,7 @@
     <s:numFmt numFmtId="165" formatCode="General"/>
     <s:numFmt numFmtId="166" formatCode="dd\.mm"/>
   </s:numFmts>
-  <s:fonts count="60">
+  <s:fonts count="61">
     <s:font>
       <s:name val="Liberation Sans"/>
       <s:color theme="1"/>
@@ -11238,6 +11840,12 @@
     </s:font>
     <s:font>
       <s:name val="Tinos"/>
+      <s:color rgb="FF000000"/>
+      <s:sz val="14"/>
+    </s:font>
+    <s:font>
+      <s:name val="Tinos"/>
+      <s:b val="1"/>
       <s:color rgb="FF000000"/>
       <s:sz val="14"/>
     </s:font>
@@ -12146,7 +12754,7 @@
   <s:cellStyleXfs count="1">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </s:cellStyleXfs>
-  <s:cellXfs count="303">
+  <s:cellXfs count="306">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <s:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <s:alignment horizontal="left" mc:Ignorable="vyd"/>
@@ -13003,6 +13611,15 @@
     </s:xf>
     <s:xf numFmtId="161" fontId="59" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <s:alignment horizontal="left" vertical="center" wrapText="1" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="161" fontId="59" borderId="82" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="164" fontId="8" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="60" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" mc:Ignorable="vyd"/>
     </s:xf>
   </s:cellXfs>
   <s:cellStyles count="1">
@@ -13226,7 +13843,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <s:sheetFormatPr defaultColWidth="10" defaultRowHeight="12.75"/>
   <s:cols>
     <s:col min="1" max="1" width="19.688" customWidth="1"/>
@@ -13235,7 +13852,7 @@
     <s:col min="4" max="4" width="40.852" customWidth="1"/>
   </s:cols>
   <s:sheetData>
-    <s:row r="1" ht="27" customHeight="1">
+    <s:row r="1" ht="32.917" customHeight="1">
       <s:c r="A1" s="297" t="s">
         <s:v>0</s:v>
       </s:c>
@@ -13243,11 +13860,11 @@
         <s:v>0</s:v>
       </s:c>
       <s:c r="C1" s="298" t="s">
-        <s:v>3473</s:v>
+        <s:v>3650</s:v>
       </s:c>
       <s:c r="D1" s="298"/>
     </s:row>
-    <s:row r="2" ht="27" customHeight="1">
+    <s:row r="2">
       <s:c r="A2" s="137" t="s">
         <s:v>3</s:v>
       </s:c>
@@ -13261,7 +13878,7 @@
         <s:v>0</s:v>
       </s:c>
     </s:row>
-    <s:row r="3" ht="27" customHeight="1">
+    <s:row r="3" ht="19.25" customHeight="1">
       <s:c r="A3" s="99" t="s">
         <s:v>6</s:v>
       </s:c>
@@ -13269,83 +13886,93 @@
       <s:c r="C3" s="99"/>
       <s:c r="D3" s="99"/>
     </s:row>
-    <s:row r="4" ht="27" customHeight="1">
-      <s:c r="A4" s="139"/>
-      <s:c r="B4" s="140"/>
-      <s:c r="C4" s="139"/>
-      <s:c r="D4" s="223"/>
+    <s:row r="4" ht="31.75" customHeight="1">
+      <s:c r="A4" s="139" t="s">
+        <s:v>21</s:v>
+      </s:c>
+      <s:c r="B4" s="140" t="s">
+        <s:v>3592</s:v>
+      </s:c>
+      <s:c r="C4" s="139" t="s">
+        <s:v>3651</s:v>
+      </s:c>
+      <s:c r="D4" s="223" t="s">
+        <s:v>10</s:v>
+      </s:c>
     </s:row>
-    <s:row r="5" ht="27" customHeight="1">
-      <s:c r="A5" s="99" t="s">
+    <s:row r="5" ht="31.75" customHeight="1">
+      <s:c r="A5" s="139" t="s">
+        <s:v>66</s:v>
+      </s:c>
+      <s:c r="B5" s="140" t="s">
+        <s:v>1907</s:v>
+      </s:c>
+      <s:c r="C5" s="139" t="s">
+        <s:v>3638</s:v>
+      </s:c>
+      <s:c r="D5" s="223" t="s">
+        <s:v>20</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="6" ht="31.75" customHeight="1">
+      <s:c r="A6" s="99" t="s">
         <s:v>831</s:v>
       </s:c>
-      <s:c r="B5" s="100"/>
-      <s:c r="C5" s="100"/>
-      <s:c r="D5" s="175"/>
+      <s:c r="B6" s="100"/>
+      <s:c r="C6" s="100"/>
+      <s:c r="D6" s="175"/>
     </s:row>
-    <s:row r="6" ht="31.688" customHeight="1">
-      <s:c r="A6" s="96" t="s">
-        <s:v>3295</s:v>
-      </s:c>
-      <s:c r="B6" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C6" s="174" t="s">
-        <s:v>3474</s:v>
-      </s:c>
-      <s:c r="D6" s="174"/>
-    </s:row>
-    <s:row r="7" ht="32.625" customHeight="1">
+    <s:row r="7" ht="30.5" customHeight="1">
       <s:c r="A7" s="96" t="s">
-        <s:v>3295</s:v>
+        <s:v>3343</s:v>
       </s:c>
       <s:c r="B7" s="96">
-        <s:v>3</s:v>
+        <s:v>1</s:v>
       </s:c>
       <s:c r="C7" s="174" t="s">
         <s:v>51</s:v>
       </s:c>
       <s:c r="D7" s="174"/>
     </s:row>
-    <s:row r="8" ht="32.625" customHeight="1">
+    <s:row r="8" ht="30.5" customHeight="1">
       <s:c r="A8" s="96" t="s">
-        <s:v>3271</s:v>
+        <s:v>3295</s:v>
       </s:c>
       <s:c r="B8" s="96">
-        <s:v>1</s:v>
+        <s:v>2</s:v>
       </s:c>
       <s:c r="C8" s="174" t="s">
-        <s:v>3297</s:v>
+        <s:v>3562</s:v>
       </s:c>
       <s:c r="D8" s="174"/>
     </s:row>
-    <s:row r="9" ht="33.563" customHeight="1">
-      <s:c r="A9" s="96" t="s">
-        <s:v>3250</s:v>
+    <s:row r="9" ht="30.5" customHeight="1">
+      <s:c r="A9" s="305" t="s">
+        <s:v>3271</s:v>
       </s:c>
       <s:c r="B9" s="96">
-        <s:v>2</s:v>
+        <s:v>1</s:v>
       </s:c>
       <s:c r="C9" s="174" t="s">
-        <s:v>3475</s:v>
+        <s:v>3653</s:v>
       </s:c>
       <s:c r="D9" s="174"/>
     </s:row>
-    <s:row r="10" ht="32.625" customHeight="1">
-      <s:c r="A10" s="96" t="s">
-        <s:v>3252</s:v>
+    <s:row r="10" ht="30.5" customHeight="1">
+      <s:c r="A10" s="305" t="s">
+        <s:v>3270</s:v>
       </s:c>
       <s:c r="B10" s="96">
-        <s:v>1</s:v>
+        <s:v>2</s:v>
       </s:c>
       <s:c r="C10" s="174" t="s">
-        <s:v>3475</s:v>
+        <s:v>3670</s:v>
       </s:c>
       <s:c r="D10" s="174"/>
     </s:row>
-    <s:row r="11" ht="33.563" customHeight="1">
-      <s:c r="A11" s="96" t="s">
-        <s:v>3252</s:v>
+    <s:row r="11" ht="30.5" customHeight="1">
+      <s:c r="A11" s="305" t="s">
+        <s:v>3272</s:v>
       </s:c>
       <s:c r="B11" s="96">
         <s:v>3</s:v>
@@ -13355,743 +13982,875 @@
       </s:c>
       <s:c r="D11" s="174"/>
     </s:row>
-    <s:row r="12" ht="33.563" customHeight="1">
-      <s:c r="A12" s="96" t="s">
-        <s:v>3276</s:v>
+    <s:row r="12" ht="30.5" customHeight="1">
+      <s:c r="A12" s="305" t="s">
+        <s:v>3251</s:v>
       </s:c>
       <s:c r="B12" s="96">
-        <s:v>3</s:v>
+        <s:v>1</s:v>
       </s:c>
       <s:c r="C12" s="174" t="s">
-        <s:v>51</s:v>
+        <s:v>3312</s:v>
       </s:c>
       <s:c r="D12" s="174"/>
     </s:row>
-    <s:row r="13" ht="33.563" customHeight="1">
+    <s:row r="13" ht="30.5" customHeight="1">
       <s:c r="A13" s="96" t="s">
-        <s:v>3253</s:v>
+        <s:v>3252</s:v>
       </s:c>
       <s:c r="B13" s="96">
         <s:v>2</s:v>
       </s:c>
       <s:c r="C13" s="174" t="s">
-        <s:v>3476</s:v>
+        <s:v>3654</s:v>
       </s:c>
       <s:c r="D13" s="174"/>
     </s:row>
-    <s:row r="14" ht="33.563" customHeight="1">
+    <s:row r="14" ht="30.5" customHeight="1">
       <s:c r="A14" s="96" t="s">
-        <s:v>3254</s:v>
+        <s:v>3252</s:v>
       </s:c>
       <s:c r="B14" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C14" s="272" t="s">
-        <s:v>3421</s:v>
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C14" s="174" t="s">
+        <s:v>51</s:v>
       </s:c>
       <s:c r="D14" s="174"/>
     </s:row>
-    <s:row r="15" ht="33.563" customHeight="1">
+    <s:row r="15" ht="30.5" customHeight="1">
       <s:c r="A15" s="96" t="s">
-        <s:v>3254</s:v>
+        <s:v>3276</s:v>
       </s:c>
       <s:c r="B15" s="96">
         <s:v>3</s:v>
       </s:c>
       <s:c r="C15" s="174" t="s">
-        <s:v>51</s:v>
+        <s:v>3653</s:v>
       </s:c>
       <s:c r="D15" s="174"/>
     </s:row>
-    <s:row r="16" ht="33.563" customHeight="1">
+    <s:row r="16" ht="31.583" customHeight="1">
       <s:c r="A16" s="96" t="s">
-        <s:v>95</s:v>
+        <s:v>104</s:v>
       </s:c>
       <s:c r="B16" s="96">
         <s:v>3</s:v>
       </s:c>
       <s:c r="C16" s="174" t="s">
-        <s:v>3477</s:v>
+        <s:v>1337</s:v>
       </s:c>
       <s:c r="D16" s="174"/>
     </s:row>
-    <s:row r="17" ht="33.563" customHeight="1">
+    <s:row r="17" ht="32.5" customHeight="1">
       <s:c r="A17" s="96" t="s">
-        <s:v>127</s:v>
+        <s:v>109</s:v>
       </s:c>
       <s:c r="B17" s="96">
         <s:v>2</s:v>
       </s:c>
       <s:c r="C17" s="174" t="s">
-        <s:v>3313</s:v>
+        <s:v>3655</s:v>
       </s:c>
       <s:c r="D17" s="174"/>
     </s:row>
-    <s:row r="18" ht="33.563" customHeight="1">
+    <s:row r="18" ht="32.5" customHeight="1">
       <s:c r="A18" s="96" t="s">
-        <s:v>110</s:v>
+        <s:v>109</s:v>
       </s:c>
       <s:c r="B18" s="96">
-        <s:v>1</s:v>
+        <s:v>3</s:v>
       </s:c>
       <s:c r="C18" s="174" t="s">
-        <s:v>3478</s:v>
+        <s:v>51</s:v>
       </s:c>
       <s:c r="D18" s="174"/>
     </s:row>
-    <s:row r="19" ht="33.563" customHeight="1">
+    <s:row r="19" ht="36.583" customHeight="1">
       <s:c r="A19" s="96" t="s">
-        <s:v>158</s:v>
+        <s:v>46</s:v>
       </s:c>
       <s:c r="B19" s="96">
-        <s:v>1</s:v>
+        <s:v>2</s:v>
       </s:c>
       <s:c r="C19" s="174" t="s">
-        <s:v>2890</s:v>
+        <s:v>3656</s:v>
       </s:c>
       <s:c r="D19" s="174"/>
     </s:row>
-    <s:row r="20" ht="33.563" customHeight="1">
+    <s:row r="20" ht="30.5" customHeight="1">
       <s:c r="A20" s="96" t="s">
-        <s:v>158</s:v>
+        <s:v>159</s:v>
       </s:c>
       <s:c r="B20" s="96">
-        <s:v>3</s:v>
+        <s:v>2</s:v>
       </s:c>
       <s:c r="C20" s="174" t="s">
-        <s:v>51</s:v>
+        <s:v>3657</s:v>
       </s:c>
       <s:c r="D20" s="174"/>
     </s:row>
-    <s:row r="21" ht="33.563" customHeight="1">
+    <s:row r="21" ht="30.5" customHeight="1">
       <s:c r="A21" s="96" t="s">
-        <s:v>55</s:v>
+        <s:v>159</s:v>
       </s:c>
       <s:c r="B21" s="96">
-        <s:v>1</s:v>
+        <s:v>3</s:v>
       </s:c>
       <s:c r="C21" s="174" t="s">
-        <s:v>1459</s:v>
+        <s:v>51</s:v>
       </s:c>
       <s:c r="D21" s="174"/>
     </s:row>
-    <s:row r="22" ht="33.563" customHeight="1">
+    <s:row r="22" ht="30.5" customHeight="1">
       <s:c r="A22" s="96" t="s">
         <s:v>55</s:v>
       </s:c>
       <s:c r="B22" s="96">
-        <s:v>2</s:v>
+        <s:v>1</s:v>
       </s:c>
       <s:c r="C22" s="174" t="s">
-        <s:v>3479</s:v>
+        <s:v>1459</s:v>
       </s:c>
       <s:c r="D22" s="174"/>
     </s:row>
-    <s:row r="23" ht="33.563" customHeight="1">
+    <s:row r="23" ht="30.5" customHeight="1">
       <s:c r="A23" s="96" t="s">
-        <s:v>131</s:v>
+        <s:v>55</s:v>
       </s:c>
       <s:c r="B23" s="96">
         <s:v>2</s:v>
       </s:c>
       <s:c r="C23" s="174" t="s">
-        <s:v>3481</s:v>
+        <s:v>3658</s:v>
       </s:c>
       <s:c r="D23" s="174"/>
     </s:row>
-    <s:row r="24" ht="37.313" customHeight="1">
-      <s:c r="A24" s="99" t="s">
+    <s:row r="24" ht="30.417" customHeight="1">
+      <s:c r="A24" s="96" t="s">
+        <s:v>115</s:v>
+      </s:c>
+      <s:c r="B24" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C24" s="174" t="s">
+        <s:v>3659</s:v>
+      </s:c>
+      <s:c r="D24" s="174"/>
+    </s:row>
+    <s:row r="25" ht="33.25" customHeight="1">
+      <s:c r="A25" s="96" t="s">
+        <s:v>115</s:v>
+      </s:c>
+      <s:c r="B25" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C25" s="174" t="s">
+        <s:v>3479</s:v>
+      </s:c>
+      <s:c r="D25" s="174"/>
+    </s:row>
+    <s:row r="26" ht="33.25" customHeight="1">
+      <s:c r="A26" s="96" t="s">
+        <s:v>57</s:v>
+      </s:c>
+      <s:c r="B26" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C26" s="174" t="s">
+        <s:v>3671</s:v>
+      </s:c>
+      <s:c r="D26" s="174"/>
+    </s:row>
+    <s:row r="27" ht="33.25" customHeight="1">
+      <s:c r="A27" s="96" t="s">
+        <s:v>62</s:v>
+      </s:c>
+      <s:c r="B27" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C27" s="174" t="s">
+        <s:v>3565</s:v>
+      </s:c>
+      <s:c r="D27" s="174"/>
+    </s:row>
+    <s:row r="28" ht="33.25" customHeight="1">
+      <s:c r="A28" s="96" t="s">
+        <s:v>62</s:v>
+      </s:c>
+      <s:c r="B28" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C28" s="174" t="s">
+        <s:v>3660</s:v>
+      </s:c>
+      <s:c r="D28" s="174"/>
+    </s:row>
+    <s:row r="29" ht="33.25" customHeight="1">
+      <s:c r="A29" s="96" t="s">
+        <s:v>73</s:v>
+      </s:c>
+      <s:c r="B29" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C29" s="174" t="s">
+        <s:v>3430</s:v>
+      </s:c>
+      <s:c r="D29" s="174"/>
+    </s:row>
+    <s:row r="30" ht="33.25" customHeight="1">
+      <s:c r="A30" s="96" t="s">
+        <s:v>73</s:v>
+      </s:c>
+      <s:c r="B30" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C30" s="174" t="s">
+        <s:v>3662</s:v>
+      </s:c>
+      <s:c r="D30" s="174"/>
+    </s:row>
+    <s:row r="31" ht="33.25" customHeight="1">
+      <s:c r="A31" s="96" t="s">
+        <s:v>73</s:v>
+      </s:c>
+      <s:c r="B31" s="96">
+        <s:v>4</s:v>
+      </s:c>
+      <s:c r="C31" s="174" t="s">
+        <s:v>51</s:v>
+      </s:c>
+      <s:c r="D31" s="174"/>
+    </s:row>
+    <s:row r="32" ht="33.25" customHeight="1">
+      <s:c r="A32" s="96" t="s">
+        <s:v>78</s:v>
+      </s:c>
+      <s:c r="B32" s="96">
+        <s:v>4</s:v>
+      </s:c>
+      <s:c r="C32" s="174" t="s">
+        <s:v>3663</s:v>
+      </s:c>
+      <s:c r="D32" s="174"/>
+    </s:row>
+    <s:row r="33" ht="33.25" customHeight="1">
+      <s:c r="A33" s="96" t="s">
+        <s:v>131</s:v>
+      </s:c>
+      <s:c r="B33" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C33" s="174" t="s">
+        <s:v>3646</s:v>
+      </s:c>
+      <s:c r="D33" s="174"/>
+    </s:row>
+    <s:row r="34" ht="33.25" customHeight="1">
+      <s:c r="A34" s="96" t="s">
+        <s:v>220</s:v>
+      </s:c>
+      <s:c r="B34" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C34" s="174" t="s">
+        <s:v>3664</s:v>
+      </s:c>
+      <s:c r="D34" s="174"/>
+    </s:row>
+    <s:row r="35" ht="34.25" customHeight="1">
+      <s:c r="A35" s="99" t="s">
         <s:v>391</s:v>
       </s:c>
-      <s:c r="B24" s="100"/>
-      <s:c r="C24" s="100"/>
-      <s:c r="D24" s="99"/>
+      <s:c r="B35" s="100"/>
+      <s:c r="C35" s="100"/>
+      <s:c r="D35" s="99"/>
     </s:row>
-    <s:row r="25" ht="27" customHeight="1">
-      <s:c r="A25" s="96" t="s">
-        <s:v>3250</s:v>
-      </s:c>
-      <s:c r="B25" s="96">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C25" s="301" t="s">
-        <s:v>821</s:v>
-      </s:c>
-      <s:c r="D25" s="174" t="s">
-        <s:v>3282</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="26" ht="27" customHeight="1">
-      <s:c r="A26" s="96" t="s">
-        <s:v>3250</s:v>
-      </s:c>
-      <s:c r="B26" s="96">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C26" s="301" t="s">
-        <s:v>1153</s:v>
-      </s:c>
-      <s:c r="D26" s="174" t="s">
-        <s:v>3285</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="27" ht="27" customHeight="1">
-      <s:c r="A27" s="96" t="s">
-        <s:v>3251</s:v>
-      </s:c>
-      <s:c r="B27" s="96">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C27" s="301" t="s">
-        <s:v>820</s:v>
-      </s:c>
-      <s:c r="D27" s="174" t="s">
-        <s:v>3303</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="28" ht="27" customHeight="1">
-      <s:c r="A28" s="96" t="s">
-        <s:v>3251</s:v>
-      </s:c>
-      <s:c r="B28" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C28" s="301" t="s">
-        <s:v>821</s:v>
-      </s:c>
-      <s:c r="D28" s="174" t="s">
-        <s:v>3282</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="29" ht="27" customHeight="1">
-      <s:c r="A29" s="96" t="s">
-        <s:v>3273</s:v>
-      </s:c>
-      <s:c r="B29" s="96">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C29" s="301" t="s">
-        <s:v>168</s:v>
-      </s:c>
-      <s:c r="D29" s="174" t="s">
-        <s:v>3284</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="30" ht="27" customHeight="1">
-      <s:c r="A30" s="96" t="s">
-        <s:v>3252</s:v>
-      </s:c>
-      <s:c r="B30" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C30" s="301" t="s">
-        <s:v>259</s:v>
-      </s:c>
-      <s:c r="D30" s="174" t="s">
-        <s:v>164</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="31" ht="27" customHeight="1">
-      <s:c r="A31" s="96" t="s">
-        <s:v>3298</s:v>
-      </s:c>
-      <s:c r="B31" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C31" s="301" t="s">
-        <s:v>1153</s:v>
-      </s:c>
-      <s:c r="D31" s="174" t="s">
-        <s:v>3285</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="32" ht="27" customHeight="1">
-      <s:c r="A32" s="96" t="s">
-        <s:v>3277</s:v>
-      </s:c>
-      <s:c r="B32" s="96">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C32" s="301" t="s">
-        <s:v>1153</s:v>
-      </s:c>
-      <s:c r="D32" s="174" t="s">
-        <s:v>3285</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="33" ht="27" customHeight="1">
-      <s:c r="A33" s="96" t="s">
-        <s:v>3278</s:v>
-      </s:c>
-      <s:c r="B33" s="96">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C33" s="301" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D33" s="174" t="s">
-        <s:v>94</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="34" ht="27" customHeight="1">
-      <s:c r="A34" s="96" t="s">
-        <s:v>95</s:v>
-      </s:c>
-      <s:c r="B34" s="96">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C34" s="301" t="s">
-        <s:v>288</s:v>
-      </s:c>
-      <s:c r="D34" s="174" t="s">
-        <s:v>3288</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="35" ht="27" customHeight="1">
-      <s:c r="A35" s="96" t="s">
-        <s:v>127</s:v>
-      </s:c>
-      <s:c r="B35" s="96">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C35" s="301" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D35" s="174" t="s">
-        <s:v>3286</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="36" ht="27" customHeight="1">
+    <s:row r="36" ht="30.5" customHeight="1">
       <s:c r="A36" s="96" t="s">
-        <s:v>101</s:v>
+        <s:v>3295</s:v>
       </s:c>
       <s:c r="B36" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C36" s="301" t="s">
-        <s:v>497</s:v>
+      <s:c r="C36" s="299" t="s">
+        <s:v>899</s:v>
       </s:c>
       <s:c r="D36" s="174" t="s">
-        <s:v>3289</s:v>
+        <s:v>3287</s:v>
       </s:c>
     </s:row>
-    <s:row r="37" ht="27" customHeight="1">
+    <s:row r="37" ht="30.5" customHeight="1">
       <s:c r="A37" s="96" t="s">
-        <s:v>104</s:v>
+        <s:v>3250</s:v>
       </s:c>
       <s:c r="B37" s="96">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="C37" s="301" t="s">
-        <s:v>497</s:v>
+      <s:c r="C37" s="299" t="s">
+        <s:v>1035</s:v>
       </s:c>
       <s:c r="D37" s="174" t="s">
-        <s:v>3289</s:v>
+        <s:v>3282</s:v>
       </s:c>
     </s:row>
-    <s:row r="38" ht="27" customHeight="1">
+    <s:row r="38" ht="30.5" customHeight="1">
       <s:c r="A38" s="96" t="s">
-        <s:v>104</s:v>
+        <s:v>3250</s:v>
       </s:c>
       <s:c r="B38" s="96">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C38" s="301" t="s">
-        <s:v>497</s:v>
+      <s:c r="C38" s="299" t="s">
+        <s:v>259</s:v>
       </s:c>
       <s:c r="D38" s="174" t="s">
-        <s:v>3289</s:v>
+        <s:v>3280</s:v>
       </s:c>
     </s:row>
-    <s:row r="39" ht="27" customHeight="1">
+    <s:row r="39" ht="30.5" customHeight="1">
       <s:c r="A39" s="96" t="s">
-        <s:v>104</s:v>
+        <s:v>3250</s:v>
       </s:c>
       <s:c r="B39" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C39" s="301" t="s">
-        <s:v>2583</s:v>
+      <s:c r="C39" s="299" t="s">
+        <s:v>3605</s:v>
       </s:c>
       <s:c r="D39" s="174" t="s">
-        <s:v>164</s:v>
+        <s:v>3285</s:v>
       </s:c>
     </s:row>
-    <s:row r="40" ht="27" customHeight="1">
+    <s:row r="40" ht="30.5" customHeight="1">
       <s:c r="A40" s="96" t="s">
-        <s:v>39</s:v>
+        <s:v>3251</s:v>
       </s:c>
       <s:c r="B40" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C40" s="299" t="s">
+        <s:v>1035</s:v>
+      </s:c>
+      <s:c r="D40" s="174" t="s">
+        <s:v>3282</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="41" ht="30.5" customHeight="1">
+      <s:c r="A41" s="96" t="s">
+        <s:v>3273</s:v>
+      </s:c>
+      <s:c r="B41" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C40" s="301" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D40" s="174" t="s">
-        <s:v>123</s:v>
+      <s:c r="C41" s="299" t="s">
+        <s:v>168</s:v>
+      </s:c>
+      <s:c r="D41" s="174" t="s">
+        <s:v>3284</s:v>
       </s:c>
     </s:row>
-    <s:row r="41" ht="27" customHeight="1">
-      <s:c r="A41" s="96" t="s">
-        <s:v>109</s:v>
-      </s:c>
-      <s:c r="B41" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C41" s="301" t="s">
-        <s:v>173</s:v>
-      </s:c>
-      <s:c r="D41" s="174" t="s">
-        <s:v>663</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="42" ht="27" customHeight="1">
+    <s:row r="42" ht="30.5" customHeight="1">
       <s:c r="A42" s="96" t="s">
-        <s:v>111</s:v>
+        <s:v>3252</s:v>
       </s:c>
       <s:c r="B42" s="96">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="C42" s="301" t="s">
-        <s:v>352</s:v>
+      <s:c r="C42" s="299" t="s">
+        <s:v>259</s:v>
       </s:c>
       <s:c r="D42" s="174" t="s">
-        <s:v>121</s:v>
+        <s:v>3280</s:v>
       </s:c>
     </s:row>
-    <s:row r="43" ht="27" customHeight="1">
+    <s:row r="43" ht="30.5" customHeight="1">
       <s:c r="A43" s="96" t="s">
-        <s:v>43</s:v>
+        <s:v>3298</s:v>
       </s:c>
       <s:c r="B43" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C43" s="299" t="s">
+        <s:v>3605</s:v>
+      </s:c>
+      <s:c r="D43" s="174" t="s">
+        <s:v>3285</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="44" ht="30.5" customHeight="1">
+      <s:c r="A44" s="96" t="s">
+        <s:v>3277</s:v>
+      </s:c>
+      <s:c r="B44" s="96">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="C43" s="301" t="s">
-        <s:v>168</s:v>
-      </s:c>
-      <s:c r="D43" s="174" t="s">
-        <s:v>824</s:v>
+      <s:c r="C44" s="299" t="s">
+        <s:v>3605</s:v>
+      </s:c>
+      <s:c r="D44" s="174" t="s">
+        <s:v>3285</s:v>
       </s:c>
     </s:row>
-    <s:row r="44" ht="27" customHeight="1">
-      <s:c r="A44" s="96" t="s">
-        <s:v>43</s:v>
-      </s:c>
-      <s:c r="B44" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C44" s="301" t="s">
-        <s:v>229</s:v>
-      </s:c>
-      <s:c r="D44" s="174" t="s">
-        <s:v>3290</s:v>
+    <s:row r="45" ht="30.5" customHeight="1">
+      <s:c r="A45" s="96" t="s">
+        <s:v>3278</s:v>
+      </s:c>
+      <s:c r="B45" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C45" s="299" t="s">
+        <s:v>93</s:v>
+      </s:c>
+      <s:c r="D45" s="174" t="s">
+        <s:v>94</s:v>
       </s:c>
     </s:row>
-    <s:row r="45" ht="27" customHeight="1">
-      <s:c r="A45" s="96" t="s">
-        <s:v>46</s:v>
-      </s:c>
-      <s:c r="B45" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C45" s="301" t="s">
+    <s:row r="46" ht="30.5" customHeight="1">
+      <s:c r="A46" s="96" t="s">
+        <s:v>95</s:v>
+      </s:c>
+      <s:c r="B46" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C46" s="299" t="s">
         <s:v>113</s:v>
       </s:c>
-      <s:c r="D45" s="174" t="s">
-        <s:v>114</s:v>
+      <s:c r="D46" s="174" t="s">
+        <s:v>3288</s:v>
       </s:c>
     </s:row>
-    <s:row r="46" ht="27" customHeight="1">
-      <s:c r="A46" s="96" t="s">
-        <s:v>48</s:v>
-      </s:c>
-      <s:c r="B46" s="96">
+    <s:row r="47" ht="30.5" customHeight="1">
+      <s:c r="A47" s="96" t="s">
+        <s:v>95</s:v>
+      </s:c>
+      <s:c r="B47" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C46" s="301" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D46" s="302" t="s">
-        <s:v>96</s:v>
+      <s:c r="C47" s="299" t="s">
+        <s:v>259</s:v>
+      </s:c>
+      <s:c r="D47" s="174" t="s">
+        <s:v>3280</s:v>
       </s:c>
     </s:row>
-    <s:row r="47" ht="27" customHeight="1">
-      <s:c r="A47" s="96" t="s">
-        <s:v>128</s:v>
-      </s:c>
-      <s:c r="B47" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C47" s="301" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D47" s="174" t="s">
-        <s:v>94</s:v>
+    <s:row r="48" ht="30.5" customHeight="1">
+      <s:c r="A48" s="96" t="s">
+        <s:v>127</s:v>
+      </s:c>
+      <s:c r="B48" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C48" s="299" t="s">
+        <s:v>102</s:v>
+      </s:c>
+      <s:c r="D48" s="174" t="s">
+        <s:v>3286</s:v>
       </s:c>
     </s:row>
-    <s:row r="48" ht="27" customHeight="1">
-      <s:c r="A48" s="96" t="s">
-        <s:v>112</s:v>
-      </s:c>
-      <s:c r="B48" s="96">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C48" s="301" t="s">
-        <s:v>462</s:v>
-      </s:c>
-      <s:c r="D48" s="174" t="s">
-        <s:v>17</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="49" ht="27" customHeight="1">
+    <s:row r="49" ht="30.5" customHeight="1">
       <s:c r="A49" s="96" t="s">
-        <s:v>112</s:v>
+        <s:v>101</s:v>
       </s:c>
       <s:c r="B49" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C49" s="301" t="s">
-        <s:v>462</s:v>
+      <s:c r="C49" s="299" t="s">
+        <s:v>821</s:v>
       </s:c>
       <s:c r="D49" s="174" t="s">
-        <s:v>17</s:v>
+        <s:v>3289</s:v>
       </s:c>
     </s:row>
-    <s:row r="50" ht="27" customHeight="1">
+    <s:row r="50" ht="30.5" customHeight="1">
       <s:c r="A50" s="96" t="s">
-        <s:v>50</s:v>
+        <s:v>104</s:v>
       </s:c>
       <s:c r="B50" s="96">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C50" s="301" t="s">
-        <s:v>228</s:v>
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C50" s="299" t="s">
+        <s:v>821</s:v>
       </s:c>
       <s:c r="D50" s="174" t="s">
-        <s:v>181</s:v>
+        <s:v>3289</s:v>
       </s:c>
     </s:row>
-    <s:row r="51" ht="27" customHeight="1">
+    <s:row r="51" ht="30.5" customHeight="1">
       <s:c r="A51" s="96" t="s">
-        <s:v>52</s:v>
+        <s:v>104</s:v>
       </s:c>
       <s:c r="B51" s="96">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C51" s="301" t="s">
-        <s:v>352</s:v>
+      <s:c r="C51" s="299" t="s">
+        <s:v>821</s:v>
       </s:c>
       <s:c r="D51" s="174" t="s">
-        <s:v>121</s:v>
+        <s:v>3289</s:v>
       </s:c>
     </s:row>
-    <s:row r="52" ht="27" customHeight="1">
+    <s:row r="52" ht="30.5" customHeight="1">
       <s:c r="A52" s="96" t="s">
-        <s:v>55</s:v>
+        <s:v>39</s:v>
       </s:c>
       <s:c r="B52" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C52" s="301" t="s">
-        <s:v>2583</s:v>
+      <s:c r="C52" s="299" t="s">
+        <s:v>116</s:v>
       </s:c>
       <s:c r="D52" s="174" t="s">
-        <s:v>3286</s:v>
+        <s:v>123</s:v>
       </s:c>
     </s:row>
-    <s:row r="53" ht="27" customHeight="1">
+    <s:row r="53" ht="30.5" customHeight="1">
       <s:c r="A53" s="96" t="s">
-        <s:v>115</s:v>
+        <s:v>111</s:v>
       </s:c>
       <s:c r="B53" s="96">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="C53" s="301" t="s">
-        <s:v>113</s:v>
+      <s:c r="C53" s="299" t="s">
+        <s:v>352</s:v>
       </s:c>
       <s:c r="D53" s="174" t="s">
-        <s:v>114</s:v>
+        <s:v>121</s:v>
       </s:c>
     </s:row>
-    <s:row r="54" ht="27" customHeight="1">
+    <s:row r="54" ht="30.5" customHeight="1">
       <s:c r="A54" s="96" t="s">
-        <s:v>115</s:v>
+        <s:v>43</s:v>
       </s:c>
       <s:c r="B54" s="96">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C54" s="301" t="s">
-        <s:v>113</s:v>
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C54" s="299" t="s">
+        <s:v>820</s:v>
       </s:c>
       <s:c r="D54" s="174" t="s">
-        <s:v>114</s:v>
+        <s:v>824</s:v>
       </s:c>
     </s:row>
-    <s:row r="55" ht="27" customHeight="1">
+    <s:row r="55" ht="30.5" customHeight="1">
       <s:c r="A55" s="96" t="s">
-        <s:v>237</s:v>
+        <s:v>43</s:v>
       </s:c>
       <s:c r="B55" s="96">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C55" s="301" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D55" s="302" t="s">
+      <s:c r="C55" s="299" t="s">
+        <s:v>462</s:v>
+      </s:c>
+      <s:c r="D55" s="174" t="s">
+        <s:v>3290</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="56" ht="30.5" customHeight="1">
+      <s:c r="A56" s="96" t="s">
+        <s:v>48</s:v>
+      </s:c>
+      <s:c r="B56" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C56" s="299" t="s">
+        <s:v>116</s:v>
+      </s:c>
+      <s:c r="D56" s="174" t="s">
         <s:v>96</s:v>
       </s:c>
     </s:row>
-    <s:row r="56" ht="27" customHeight="1">
-      <s:c r="A56" s="96" t="s">
-        <s:v>60</s:v>
-      </s:c>
-      <s:c r="B56" s="96">
+    <s:row r="57" ht="30.5" customHeight="1">
+      <s:c r="A57" s="96" t="s">
+        <s:v>128</s:v>
+      </s:c>
+      <s:c r="B57" s="96">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C56" s="301" t="s">
+      <s:c r="C57" s="299" t="s">
+        <s:v>93</s:v>
+      </s:c>
+      <s:c r="D57" s="174" t="s">
+        <s:v>94</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="58" ht="30.5" customHeight="1">
+      <s:c r="A58" s="96" t="s">
+        <s:v>112</s:v>
+      </s:c>
+      <s:c r="B58" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C58" s="299" t="s">
         <s:v>3292</s:v>
       </s:c>
-      <s:c r="D56" s="174" t="s">
-        <s:v>224</s:v>
+      <s:c r="D58" s="174" t="s">
+        <s:v>17</s:v>
       </s:c>
     </s:row>
-    <s:row r="57" ht="27" customHeight="1">
-      <s:c r="A57" s="241" t="s">
-        <s:v>62</s:v>
-      </s:c>
-      <s:c r="B57" s="96">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C57" s="301" t="s">
-        <s:v>229</s:v>
-      </s:c>
-      <s:c r="D57" s="174" t="s">
-        <s:v>3290</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="58" ht="27" customHeight="1">
-      <s:c r="A58" s="241" t="s">
-        <s:v>187</s:v>
-      </s:c>
-      <s:c r="B58" s="96">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C58" s="301" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D58" s="302" t="s">
-        <s:v>96</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="59" ht="27" customHeight="1">
-      <s:c r="A59" s="241" t="s">
-        <s:v>187</s:v>
+    <s:row r="59" ht="30.5" customHeight="1">
+      <s:c r="A59" s="96" t="s">
+        <s:v>112</s:v>
       </s:c>
       <s:c r="B59" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C59" s="301" t="s">
-        <s:v>229</s:v>
+      <s:c r="C59" s="299" t="s">
+        <s:v>3292</s:v>
       </s:c>
       <s:c r="D59" s="174" t="s">
-        <s:v>3290</s:v>
+        <s:v>17</s:v>
       </s:c>
     </s:row>
-    <s:row r="60" ht="27" customHeight="1">
-      <s:c r="A60" s="241" t="s">
-        <s:v>71</s:v>
+    <s:row r="60" ht="30.5" customHeight="1">
+      <s:c r="A60" s="96" t="s">
+        <s:v>50</s:v>
       </s:c>
       <s:c r="B60" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C60" s="299" t="s">
+        <s:v>3668</s:v>
+      </s:c>
+      <s:c r="D60" s="174" t="s">
+        <s:v>1966</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="61" ht="30.5" customHeight="1">
+      <s:c r="A61" s="96" t="s">
+        <s:v>50</s:v>
+      </s:c>
+      <s:c r="B61" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C60" s="301" t="s">
-        <s:v>1322</s:v>
-      </s:c>
-      <s:c r="D60" s="174" t="s">
-        <s:v>3291</s:v>
+      <s:c r="C61" s="299" t="s">
+        <s:v>3666</s:v>
+      </s:c>
+      <s:c r="D61" s="174" t="s">
+        <s:v>181</s:v>
       </s:c>
     </s:row>
-    <s:row r="61" ht="27" customHeight="1">
-      <s:c r="A61" s="241" t="s">
-        <s:v>73</s:v>
-      </s:c>
-      <s:c r="B61" s="96">
+    <s:row r="62" ht="30.5" customHeight="1">
+      <s:c r="A62" s="96" t="s">
+        <s:v>52</s:v>
+      </s:c>
+      <s:c r="B62" s="96">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C61" s="301" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D61" s="174" t="s">
-        <s:v>3286</s:v>
+      <s:c r="C62" s="299" t="s">
+        <s:v>352</s:v>
+      </s:c>
+      <s:c r="D62" s="174" t="s">
+        <s:v>121</s:v>
       </s:c>
     </s:row>
-    <s:row r="62" ht="27" customHeight="1">
-      <s:c r="A62" s="241" t="s">
-        <s:v>75</s:v>
-      </s:c>
-      <s:c r="B62" s="96">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C62" s="301" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D62" s="174" t="s">
-        <s:v>123</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="63" ht="27" customHeight="1">
-      <s:c r="A63" s="241" t="s">
-        <s:v>75</s:v>
+    <s:row r="63" ht="30.5" customHeight="1">
+      <s:c r="A63" s="96" t="s">
+        <s:v>55</s:v>
       </s:c>
       <s:c r="B63" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C63" s="301" t="s">
-        <s:v>352</s:v>
+      <s:c r="C63" s="299" t="s">
+        <s:v>102</s:v>
       </s:c>
       <s:c r="D63" s="174" t="s">
-        <s:v>121</s:v>
+        <s:v>3286</s:v>
       </s:c>
     </s:row>
-    <s:row r="64" ht="27" customHeight="1">
-      <s:c r="A64" s="241" t="s">
-        <s:v>80</s:v>
+    <s:row r="64" ht="30.5" customHeight="1">
+      <s:c r="A64" s="96" t="s">
+        <s:v>237</s:v>
       </s:c>
       <s:c r="B64" s="96">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C64" s="301" t="s">
-        <s:v>2583</s:v>
+      <s:c r="C64" s="299" t="s">
+        <s:v>116</s:v>
       </s:c>
       <s:c r="D64" s="174" t="s">
+        <s:v>96</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="65" ht="30.5" customHeight="1">
+      <s:c r="A65" s="96" t="s">
+        <s:v>60</s:v>
+      </s:c>
+      <s:c r="B65" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C65" s="299" t="s">
+        <s:v>229</s:v>
+      </s:c>
+      <s:c r="D65" s="174" t="s">
+        <s:v>224</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="66" ht="30.5" customHeight="1">
+      <s:c r="A66" s="96" t="s">
+        <s:v>62</s:v>
+      </s:c>
+      <s:c r="B66" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C66" s="299" t="s">
+        <s:v>117</s:v>
+      </s:c>
+      <s:c r="D66" s="174" t="s">
+        <s:v>3290</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="67" ht="30.5" customHeight="1">
+      <s:c r="A67" s="96" t="s">
+        <s:v>187</s:v>
+      </s:c>
+      <s:c r="B67" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C67" s="299" t="s">
+        <s:v>116</s:v>
+      </s:c>
+      <s:c r="D67" s="174" t="s">
+        <s:v>96</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="68" ht="30.5" customHeight="1">
+      <s:c r="A68" s="96" t="s">
+        <s:v>187</s:v>
+      </s:c>
+      <s:c r="B68" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C68" s="299" t="s">
+        <s:v>462</s:v>
+      </s:c>
+      <s:c r="D68" s="174" t="s">
+        <s:v>3290</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="69" ht="30.5" customHeight="1">
+      <s:c r="A69" s="96" t="s">
+        <s:v>71</s:v>
+      </s:c>
+      <s:c r="B69" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C69" s="299" t="s">
+        <s:v>113</s:v>
+      </s:c>
+      <s:c r="D69" s="174" t="s">
+        <s:v>3291</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="70" ht="30.5" customHeight="1">
+      <s:c r="A70" s="96" t="s">
+        <s:v>73</s:v>
+      </s:c>
+      <s:c r="B70" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C70" s="299" t="s">
+        <s:v>102</s:v>
+      </s:c>
+      <s:c r="D70" s="174" t="s">
+        <s:v>3286</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="71" ht="30.5" customHeight="1">
+      <s:c r="A71" s="96" t="s">
+        <s:v>75</s:v>
+      </s:c>
+      <s:c r="B71" s="96">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="C71" s="299" t="s">
+        <s:v>116</s:v>
+      </s:c>
+      <s:c r="D71" s="174" t="s">
         <s:v>123</s:v>
       </s:c>
     </s:row>
-    <s:row r="65" ht="27" customHeight="1">
-      <s:c r="A65" s="241" t="s">
+    <s:row r="72" ht="30.5" customHeight="1">
+      <s:c r="A72" s="96" t="s">
+        <s:v>75</s:v>
+      </s:c>
+      <s:c r="B72" s="96">
+        <s:v>3</s:v>
+      </s:c>
+      <s:c r="C72" s="299" t="s">
+        <s:v>352</s:v>
+      </s:c>
+      <s:c r="D72" s="174" t="s">
+        <s:v>3667</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="73" ht="30.5" customHeight="1">
+      <s:c r="A73" s="96" t="s">
+        <s:v>78</s:v>
+      </s:c>
+      <s:c r="B73" s="96">
+        <s:v>2.3</s:v>
+      </s:c>
+      <s:c r="C73" s="299" t="s">
+        <s:v>3668</s:v>
+      </s:c>
+      <s:c r="D73" s="174" t="s">
+        <s:v>1966</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="74" ht="30.5" customHeight="1">
+      <s:c r="A74" s="96" t="s">
+        <s:v>80</s:v>
+      </s:c>
+      <s:c r="B74" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C74" s="299" t="s">
+        <s:v>116</s:v>
+      </s:c>
+      <s:c r="D74" s="174" t="s">
+        <s:v>123</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="75" ht="30.5" customHeight="1">
+      <s:c r="A75" s="96" t="s">
+        <s:v>131</s:v>
+      </s:c>
+      <s:c r="B75" s="96">
+        <s:v>2</s:v>
+      </s:c>
+      <s:c r="C75" s="299" t="s">
+        <s:v>1217</s:v>
+      </s:c>
+      <s:c r="D75" s="174" t="s">
+        <s:v>3293</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="76" ht="30.5" customHeight="1">
+      <s:c r="A76" s="96" t="s">
         <s:v>220</s:v>
       </s:c>
-      <s:c r="B65" s="96">
+      <s:c r="B76" s="96">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="C65" s="301" t="s">
-        <s:v>2583</s:v>
-      </s:c>
-      <s:c r="D65" s="174" t="s">
+      <s:c r="C76" s="299" t="s">
+        <s:v>93</s:v>
+      </s:c>
+      <s:c r="D76" s="174" t="s">
         <s:v>94</s:v>
       </s:c>
     </s:row>
-    <s:row r="66" ht="27" customHeight="1">
-      <s:c r="A66" s="241" t="s">
+    <s:row r="77" ht="30.5" customHeight="1">
+      <s:c r="A77" s="96" t="s">
         <s:v>220</s:v>
       </s:c>
-      <s:c r="B66" s="96">
+      <s:c r="B77" s="96">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C66" s="301" t="s">
-        <s:v>821</s:v>
-      </s:c>
-      <s:c r="D66" s="174" t="s">
+      <s:c r="C77" s="299" t="s">
+        <s:v>1035</s:v>
+      </s:c>
+      <s:c r="D77" s="174" t="s">
         <s:v>3282</s:v>
       </s:c>
     </s:row>
@@ -14099,8 +14858,8 @@
   <s:mergeCells count="4">
     <s:mergeCell ref="C1:D1"/>
     <s:mergeCell ref="A3:D3"/>
-    <s:mergeCell ref="A5:D5"/>
-    <s:mergeCell ref="A24:D24"/>
+    <s:mergeCell ref="A6:D6"/>
+    <s:mergeCell ref="A35:D35"/>
   </s:mergeCells>
   <s:printOptions headings="0" gridLines="0"/>
   <s:pageMargins left="0.701" right="0.701" top="0.752" bottom="0.752" header="0.3" footer="0.3"/>
